--- a/Data Product XWORLD.xlsx
+++ b/Data Product XWORLD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Laravel\xanhworld.vn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31C9A6F-B789-4C8B-80D4-6364D9A7EC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A56623-2CE3-4F35-8010-0F476497B118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="images" sheetId="2" r:id="rId2"/>
     <sheet name="faqs" sheetId="3" r:id="rId3"/>
     <sheet name="how_tos" sheetId="4" r:id="rId4"/>
+    <sheet name="variants" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="355">
   <si>
     <t>sku</t>
   </si>
@@ -239,6 +240,9 @@
     <t>cây phát tài,cây phong thủy phát tài,cây phát tài núi,cây phát tài phát lộc,cây phát tài đỏ,cây phát tài búp sen,thiết mộc lan,cây kim tiền,cây cảnh phong thủy,mua cây phát tài</t>
   </si>
   <si>
+    <t>https://xanhworld.vn/san-pham/cay-phat-tai-cay-canh-phong-thuy-thu-hut-tai-loc</t>
+  </si>
+  <si>
     <t>cay-phong-thuy</t>
   </si>
   <si>
@@ -251,146 +255,13 @@
     <t>IMG1,IMG2,IMG3,IMG4</t>
   </si>
   <si>
-    <t>image_key</t>
-  </si>
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>alt</t>
-  </si>
-  <si>
-    <t>is_primary</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>IMG1</t>
-  </si>
-  <si>
-    <t>cay-phat-tai-de-ban-gia-tot.webp</t>
-  </si>
-  <si>
-    <t>IMG2</t>
-  </si>
-  <si>
-    <t>cay-phat-tai-1.webp</t>
-  </si>
-  <si>
-    <t>IMG3</t>
-  </si>
-  <si>
-    <t>cay-phat-tai.webp</t>
-  </si>
-  <si>
-    <t>IMG4</t>
-  </si>
-  <si>
-    <t>cay-phat-tai-khuc-bo-3-nho.webp</t>
-  </si>
-  <si>
-    <t>question</t>
-  </si>
-  <si>
-    <t>answer</t>
-  </si>
-  <si>
-    <t>Cây phát tài có ý nghĩa gì trong phong thủy?</t>
-  </si>
-  <si>
-    <t>Cây phát tài tượng trưng cho tài lộc, may mắn, vượng khí và sự thịnh vượng. Cây phù hợp đặt tại nhà ở, văn phòng, cửa hàng kinh doanh để thu hút năng lượng tích cực.</t>
-  </si>
-  <si>
-    <t>Cây phát tài hợp mệnh gì?</t>
-  </si>
-  <si>
-    <t>Tùy từng loại:
-Phát tài núi hợp mệnh Thủy – Mộc – Hỏa
-Phát lộc hợp mệnh Kim
-Phát tài đỏ hợp mệnh Hỏa
-Búp sen hợp mệnh Kim – Mộc – Thủy
-Hầu hết các loại đều phù hợp nhiều mệnh trong ngũ hành.</t>
-  </si>
-  <si>
-    <t>Cây phát tài chăm sóc có khó không?</t>
-  </si>
-  <si>
-    <t>Không. Cây rất dễ chăm: sống tốt trong môi trường thiếu sáng, chỉ cần tưới nước định kỳ và thỉnh thoảng tắm nắng nhẹ để cây xanh tốt.</t>
-  </si>
-  <si>
-    <t>Cây phát tài nên đặt ở vị trí nào?</t>
-  </si>
-  <si>
-    <t>Theo phong thủy, nên đặt ở hướng Đông hoặc Đông Nam để thu hút tài lộc. Trong thực tế có thể đặt ở bàn làm việc, phòng khách, quầy lễ tân, lối vào cửa hàng.</t>
-  </si>
-  <si>
-    <t>Bao lâu nên thay chậu cho cây phát tài?</t>
-  </si>
-  <si>
-    <t>Thông thường 1 năm thay chậu 1 lần để giúp bộ rễ phát triển khỏe, đất tơi xốp, thoát nước tốt hơn.</t>
-  </si>
-  <si>
-    <t>Cây phát tài có độc không?</t>
-  </si>
-  <si>
-    <t>Đa số các loại không độc. Một số ít có thể gây kích ứng nhẹ nếu nhựa cây dính vào da, chỉ cần rửa sạch sau khi cắt tỉa.</t>
-  </si>
-  <si>
-    <t>Cây phát tài giá bao nhiêu?</t>
-  </si>
-  <si>
-    <t>Tùy loại và kích thước:
-Từ 70.000đ đến khoảng 3.000.000đ
-Giá cao hơn đối với cây lớn, lâu năm hoặc tạo dáng phong thủy.</t>
-  </si>
-  <si>
-    <t>Cây phát tài trồng thủy sinh được không?</t>
-  </si>
-  <si>
-    <t>Có. Một số loại như phát tài búp sen hoặc phát lộc rất phù hợp trồng thủy sinh, dễ chăm, sạch đẹp.</t>
-  </si>
-  <si>
-    <t>Cây phát tài ra hoa có ý nghĩa gì?</t>
-  </si>
-  <si>
-    <t>Cây phát tài ra hoa được xem là dấu hiệu tài lộc – vận may đang đến. Đây là hiện tượng hiếm gặp và được xem là điềm tốt.</t>
-  </si>
-  <si>
-    <t>Tôi mới bắt đầu chơi cây, có nên mua cây phát tài không?</t>
-  </si>
-  <si>
-    <t>Rất phù hợp. Cây dễ trồng, ít sâu bệnh, chăm sóc đơn giản và mang ý nghĩa phong thủy tốt, phù hợp cả người mới chơi.</t>
-  </si>
-  <si>
-    <t>steps</t>
-  </si>
-  <si>
-    <t>supplies</t>
-  </si>
-  <si>
-    <t>Cách chăm sóc cây Phát Tài để cây luôn xanh tốt và thu hút tài lộc</t>
-  </si>
-  <si>
-    <t>Hướng dẫn các bước chăm sóc cây Phát Tài đúng cách để cây phát triển khỏe, lá xanh đẹp và mang lại năng lượng phong thủy tích cực cho ngôi nhà bạn.</t>
-  </si>
-  <si>
-    <t>["Bước 1: Đặt cây ở vị trí có ánh sáng nhẹ, tránh nắng gắt trực tiếp.","Bước 2: Tưới nước giữ ẩm vừa phải, không để đất bị úng.","Bước 3: Phun sương lên lá 2–3 lần mỗi tuần để cây quang hợp tốt.","Bước 4: Bón phân hữu cơ hoặc NPK loãng mỗi 1–2 tháng.","Bước 5: Tỉa bỏ lá vàng, thay chậu định kỳ 1 năm\/lần để cây phát triển khỏe."]</t>
-  </si>
-  <si>
-    <t>["Dụng cụ 1: Bình tưới nước hoặc bình phun sương","Dụng cụ 2: Phân bón hữu cơ hoặc NPK","Dụng cụ 3: Kéo cắt tỉa lá","Dụng cụ 4: Đất trồng tơi xốp, thoát nước tốt (nếu thay chậu)"]</t>
-  </si>
-  <si>
-    <t>https://xanhworld.vn/san-pham/cay-phat-tai-cay-canh-phong-thuy-thu-hut-tai-loc</t>
-  </si>
-  <si>
     <t>XWCKT120625</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền – Ý Nghĩa Phong Thủy, Cách Chăm Sóc và Giá Tham Khảo</t>
+  </si>
+  <si>
+    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao</t>
   </si>
   <si>
     <t>&lt;h2 style="color:#3bb77e; font-weight:bold; margin-top:20px;"&gt;
@@ -550,192 +421,24 @@
 &lt;/div&gt;</t>
   </si>
   <si>
-    <t>Cây Kim Tiền – Ý Nghĩa Phong Thủy, Cách Chăm Sóc và Giá Tham Khảo</t>
-  </si>
-  <si>
     <t>Cây Kim Tiền: Ý Nghĩa Phong Thủy, Cách Chăm Sóc, Giá Tham Khảo Chi Tiết</t>
   </si>
   <si>
     <t>Cây Kim Tiền (Kim Phát Tài) – biểu tượng phong thủy may mắn, tài lộc và thịnh vượng. Tìm hiểu đặc điểm, ý nghĩa, cách chăm sóc, vị trí đặt cây và bảng giá tham khảo chi tiết.</t>
   </si>
   <si>
-    <t>cây kim tiền, kim phát tài, cây kim tiền phong thủy, ý nghĩa cây kim tiền, chăm sóc cây kim tiền, giá cây kim tiền, cây kim phát tài, cây phong thủy văn phòng, cây xanh trong nhà</t>
-  </si>
-  <si>
-    <t>cây kim tiền, phong thủy, cây xanh văn phòng, cây cảnh trong nhà, cây để bàn, tài lộc, thịnh vượng</t>
-  </si>
-  <si>
-    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao</t>
+    <t>cây kim tiền,kim phát tài,cây kim tiền phong thủy,ý nghĩa cây kim tiền,chăm sóc cây kim tiền,giá cây kim tiền,cây kim phát tài,cây phong thủy văn phòng,cây xanh trong nhà</t>
   </si>
   <si>
     <t>https://xanhworld.vn/san-pham/cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao</t>
   </si>
   <si>
-    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao.webp</t>
-  </si>
-  <si>
-    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao-1.webp</t>
-  </si>
-  <si>
-    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao-2.webp</t>
-  </si>
-  <si>
-    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao-3.webp</t>
-  </si>
-  <si>
-    <t>IMG5</t>
-  </si>
-  <si>
-    <t>IMG6</t>
-  </si>
-  <si>
-    <t>IMG7</t>
-  </si>
-  <si>
-    <t>IMG8</t>
+    <t>cây kim tiền,phong thủy,cây xanh văn phòng,cây cảnh trong nhà,cây để bàn,tài lộc,thịnh vượng</t>
   </si>
   <si>
     <t>IMG5,IMG6,IMG7,IMG8</t>
   </si>
   <si>
-    <t>Cây Kim Tiền có ý nghĩa gì trong phong thủy?</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền tượng trưng cho tài lộc, may mắn, sự thịnh vượng và phát triển. Đây là loại cây được tin rằng mang đến nguồn năng lượng tích cực, giúp thu hút tiền bạc và vận khí tốt.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền hợp mệnh gì?</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền thuộc hành Mộc, rất hợp với người mệnh Mộc và Hỏa. Tuy nhiên hầu hết các mệnh khác vẫn có thể trồng vì cây mang tính trung hòa, dễ dung hòa với không gian sống.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền có dễ chăm sóc không?</t>
-  </si>
-  <si>
-    <t>Rất dễ. Cây chịu bóng tốt, sống khỏe trong môi trường máy lạnh, chỉ cần tưới nước vừa phải và giữ đất thoát nước tốt.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền nên đặt ở đâu để hút tài lộc?</t>
-  </si>
-  <si>
-    <t>Phong thủy khuyên đặt ở hướng Đông hoặc Đông Nam để kích hoạt tài lộc. Trong thực tế có thể đặt tại bàn làm việc, phòng khách, quầy lễ tân hoặc cửa hàng kinh doanh.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền bao lâu thì nên thay chậu?</t>
-  </si>
-  <si>
-    <t>Thường 1–2 năm thay chậu một lần vì bộ rễ của cây phát triển mạnh. Việc thay chậu giúp đất tơi xốp hơn và cây sinh trưởng tốt.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền có độc không?</t>
-  </si>
-  <si>
-    <t>Cây không độc nhưng nhựa cây có thể gây kích ứng nhẹ nếu dính vào da. Khi cắt tỉa chỉ cần rửa tay sạch là được.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền giá bao nhiêu?</t>
-  </si>
-  <si>
-    <t>Tùy kích thước và dáng cây:_x000D_
-_x000D_
-15–30cm: 70.000đ – 100.000đ_x000D_
-30–50cm: 200.000đ – 350.000đ_x000D_
-Trên 50cm: 350.000đ – 500.000đ_x000D_
-_x000D_
-Giá thay đổi theo chậu, chất lượng rễ và dáng cây.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền có trồng thủy sinh được không?</t>
-  </si>
-  <si>
-    <t>Có. Cây Kim Tiền trồng thủy sinh rất đẹp, sạch và dễ chăm, chỉ cần thay nước định kỳ và đặt nơi có ánh sáng nhẹ.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền ra hoa có ý nghĩa gì?</t>
-  </si>
-  <si>
-    <t>Kim Tiền ra hoa được xem là điềm cực kỳ may mắn, báo hiệu tài lộc và cơ hội mới đang đến. Đây là hiện tượng hiếm gặp và mang ý nghĩa tốt lành.</t>
-  </si>
-  <si>
-    <t>Tại sao cây Kim Tiền bị vàng lá?</t>
-  </si>
-  <si>
-    <t>Nguyên nhân thường gặp: tưới quá nhiều nước, đất bí, thiếu ánh sáng, hoặc cây bị nấm rễ. Cần kiểm tra độ ẩm đất và điều chỉnh ánh sáng, đồng thời cắt bỏ lá vàng.</t>
-  </si>
-  <si>
-    <t>Cách tưới nước cho cây Kim Tiền thế nào là đúng?</t>
-  </si>
-  <si>
-    <t>Tưới 1–2 lần/tuần bằng cách phun sương khi đất còn ẩm. Không tưới quá nhiều vì cây chịu úng rất kém. Mỗi tháng có thể tưới đẫm một lần.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền có sống được trong phòng lạnh không?</t>
-  </si>
-  <si>
-    <t>Có. Cây sống rất tốt trong môi trường máy lạnh, văn phòng hoặc nơi ít ánh sáng.</t>
-  </si>
-  <si>
-    <t>Nên dùng đất gì để trồng cây Kim Tiền?</t>
-  </si>
-  <si>
-    <t>Dùng đất tơi xốp, thoát nước tốt như đất mùn, trộn thêm trấu hun, xơ dừa hoặc xỉ than giúp hạn chế úng rễ.</t>
-  </si>
-  <si>
-    <t>Bao lâu nên bón phân cho cây Kim Tiền?</t>
-  </si>
-  <si>
-    <t>2–3 tháng bón phân một lần. Dùng phân hữu cơ hoặc phân NPK dành cho cây cảnh, rải cách gốc khoảng 10–15cm.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền có cần ánh sáng không?</t>
-  </si>
-  <si>
-    <t>Có, nhưng chỉ cần ánh sáng gián tiếp. Tránh để dưới nắng gắt vì có thể khiến lá cháy mép.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền có hợp đặt ở quầy thu ngân không?</t>
-  </si>
-  <si>
-    <t>Rất hợp. Đây là vị trí giúp thu hút tài lộc theo quan niệm phong thủy, thường thấy ở cửa hàng, spa và doanh nghiệp.</t>
-  </si>
-  <si>
-    <t>Cây Kim Tiền có thể để trên bàn làm việc không?</t>
-  </si>
-  <si>
-    <t>Được. Kích thước nhỏ từ 15–30cm rất phù hợp đặt bàn, giúp mang đến cảm giác xanh mát và may mắn trong công việc.</t>
-  </si>
-  <si>
-    <t>Cách nhân giống cây Kim Tiền như thế nào?</t>
-  </si>
-  <si>
-    <t>Có thể nhân giống bằng cành hoặc bằng lá. Cắt lá hoặc cành khỏe, để khô vài giờ rồi cắm vào đất ẩm. Sau 1 tháng cây sẽ ra rễ mới.</t>
-  </si>
-  <si>
-    <t>Vì sao đất trồng cây Kim Tiền có mùi hoặc bị nấm?</t>
-  </si>
-  <si>
-    <t>Do tưới quá nhiều hoặc chậu không thoát nước tốt. Cần thay đất mới và giảm lượng nước tưới.</t>
-  </si>
-  <si>
-    <t>Người mới chơi cây có nên chọn cây Kim Tiền không?</t>
-  </si>
-  <si>
-    <t>Rất nên. Đây là loại cây dễ trồng nhất trong nhóm cây phong thủy, ít sâu bệnh, sống khỏe và mang nhiều ý nghĩa tốt lành.</t>
-  </si>
-  <si>
-    <t>Cách chăm sóc cây Kim Tiền để cây luôn xanh mướt và hút tài lộc</t>
-  </si>
-  <si>
-    <t>Hướng dẫn các bước chăm sóc cây Kim Tiền đúng cách để cây phát triển khỏe mạnh, lá bóng đẹp và mang lại tài lộc – may mắn cho không gian sống.</t>
-  </si>
-  <si>
-    <t>["Bước 1: Đặt cây ở nơi có ánh sáng gián tiếp, tránh nắng gắt chiếu trực tiếp vào lá.","Bước 2: Tưới nước 1–2 lần/tuần bằng cách phun sương, chỉ tưới thêm khi đất khô bề mặt.","Bước 3: Duy trì độ thoáng cho đất, tránh để cây bị úng rễ bằng cách dùng chậu thoát nước tốt.","Bước 4: Bón phân hữu cơ hoặc phân chậm tan 2–3 tháng/lần để cây phát triển ổn định.","Bước 5: Lau sạch lá mỗi tuần và cắt bỏ lá vàng để hạn chế sâu bệnh và giữ cây xanh đẹp.","Bước 6: Thay chậu định kỳ 1–2 năm/lần giúp bộ rễ phát triển mạnh hơn."]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">["Dụng cụ 1: Bình phun sương hoặc bình tưới","Dụng cụ 2: Đất trồng tơi xốp, thoát nước tốt","Dụng cụ 3: Phân hữu cơ hoặc phân NPK chậm tan","Dụng cụ 4: Khăn mềm để lau lá","Dụng cụ 5: Kéo cắt tỉa"] </t>
-  </si>
-  <si>
     <t>XWCLH061225</t>
   </si>
   <si>
@@ -743,162 +446,6 @@
   </si>
   <si>
     <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ: Ý Nghĩa Phong Thủy, Công Dụng, Cách Chăm Sóc Chi Tiết</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ – loại cây phong thủy nổi bật với khả năng thanh lọc không khí, hút tài lộc và mang lại năng lượng tích cực. Tìm hiểu ý nghĩa, cách chăm sóc và công dụng chi tiết của cây Lưỡi Hổ.</t>
-  </si>
-  <si>
-    <t>cây lưỡi hổ, ý nghĩa cây lưỡi hổ, công dụng cây lưỡi hổ, chăm sóc cây lưỡi hổ, cây phong thủy trong nhà, cây hút tài lộc, cây lọc không khí, lưỡi hổ phong thủy, cây để bàn dễ chăm</t>
-  </si>
-  <si>
-    <t>cây lưỡi hổ, cây phong thủy, cây lọc không khí, cây trong nhà, cây để bàn, tài lộc, bảo vệ sức khỏe</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ có ý nghĩa gì trong phong thủy?</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ tượng trưng cho sức mạnh, sự bảo vệ, xua đuổi năng lượng xấu và thu hút tài lộc. Là cây mang lại nguồn năng lượng dương mạnh mẽ cho không gian sống.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ hợp mệnh gì?</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ thuộc hành Mộc nhưng lại mang nét Kim do dáng lá sắc nhọn, vì vậy hợp với mệnh Kim, Mộc, Thổ.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ có lọc không khí không?</t>
-  </si>
-  <si>
-    <t>Có. Đây là một trong những loại cây được NASA công nhận có khả năng lọc khí độc như formaldehyde, benzene, toluene và biến CO₂ thành O₂ vào ban đêm.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ có dễ chăm không?</t>
-  </si>
-  <si>
-    <t>Rất dễ. Cây ưa khô, chịu hạn tốt, chỉ cần tưới 1 lần/tuần và đặt nơi có ánh sáng nhẹ.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ nên đặt ở đâu?</t>
-  </si>
-  <si>
-    <t>Có thể đặt ở phòng khách, phòng ngủ, văn phòng, cửa hàng hoặc nơi có nguồn khí không tốt để cân bằng năng lượng.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ có sống được trong phòng máy lạnh không?</t>
-  </si>
-  <si>
-    <t>Có. Cây sống tốt trong môi trường khô và ít sáng, rất phù hợp văn phòng.</t>
-  </si>
-  <si>
-    <t>Tưới nước cho cây Lưỡi Hổ thế nào là đúng?</t>
-  </si>
-  <si>
-    <t>Tưới 1 lần/7–10 ngày. Không tưới quá nhiều vì dễ gây úng rễ.</t>
-  </si>
-  <si>
-    <t>Tại sao lá Lưỡi Hổ bị nhăn hoặc mềm?</t>
-  </si>
-  <si>
-    <t>Do tưới quá nhiều hoặc đất bị nén chặt khiến rễ không thoáng khí. Cần thay đất hoặc giảm tưới.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ để phòng ngủ được không?</t>
-  </si>
-  <si>
-    <t>Được. Cây nhả oxy vào ban đêm, rất tốt cho đường hô hấp.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ có độc không?</t>
-  </si>
-  <si>
-    <t>Cây không độc nhưng nhựa của lá có thể gây kích ứng nhẹ khi nuốt hoặc tiếp xúc trực tiếp. Nên đặt xa trẻ nhỏ và thú cưng.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ giá bao nhiêu?</t>
-  </si>
-  <si>
-    <t>Giá dao động từ 50.000đ đến 500.000đ tùy kích thước và số lượng bụi.</t>
-  </si>
-  <si>
-    <t>Bao lâu nên thay chậu cho cây Lưỡi Hổ?</t>
-  </si>
-  <si>
-    <t>1–2 năm thay chậu một lần để bộ rễ phát triển mạnh và đất tơi xốp hơn.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ có nhân giống được không?</t>
-  </si>
-  <si>
-    <t>Được. Có thể tách bụi hoặc cắt lá để nhân giống.</t>
-  </si>
-  <si>
-    <t>Vì sao lá Lưỡi Hổ bị cháy mép?</t>
-  </si>
-  <si>
-    <t>Do ánh nắng gắt chiếu trực tiếp hoặc thiếu nước trong thời gian dài.</t>
-  </si>
-  <si>
-    <t>Cây Lưỡi Hổ có đặt ở bàn làm việc được không?</t>
-  </si>
-  <si>
-    <t>Hoàn toàn được. Đây là cây phong thủy giúp tăng sự tập trung và xua đuổi khí xấu.</t>
-  </si>
-  <si>
-    <t>Cách chăm sóc cây Lưỡi Hổ để cây luôn khỏe mạnh và lọc không khí tốt</t>
-  </si>
-  <si>
-    <t>Hướng dẫn các bước chăm sóc cây Lưỡi Hổ đúng kỹ thuật để cây sinh trưởng mạnh, lá cứng đẹp và phát huy tối đa khả năng thanh lọc không khí.</t>
-  </si>
-  <si>
-    <t>["Bước 1: Đặt cây ở nơi có ánh sáng nhẹ hoặc ánh sáng gián tiếp.","Bước 2: Tưới nước 7–10 ngày/lần, chỉ tưới khi đất khô hoàn toàn.","Bước 3: Sử dụng đất tơi xốp, thoát nước tốt để tránh úng rễ.","Bước 4: Lau lá 1 lần/tuần giúp cây quang hợp hiệu quả.","Bước 5: Bón phân hữu cơ hoặc phân tan chậm mỗi 2–3 tháng.","Bước 6: Thay chậu định kỳ 1–2 năm/lần khi cây mọc nhiều bụi."]</t>
-  </si>
-  <si>
-    <t>["Dụng cụ 1: Bình tưới hoặc bình phun sương","Dụng cụ 2: Đất tơi xốp – thoát nước tốt","Dụng cụ 3: Phân hữu cơ hoặc phân tan chậm","Dụng cụ 4: Khăn mềm để lau lá","Dụng cụ 5: Kéo cắt tỉa hoặc dụng cụ tách bụi"]</t>
-  </si>
-  <si>
-    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-2.webp</t>
-  </si>
-  <si>
-    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung.webp</t>
-  </si>
-  <si>
-    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-1.webp</t>
-  </si>
-  <si>
-    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-3.webp</t>
-  </si>
-  <si>
-    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-4.webp</t>
-  </si>
-  <si>
-    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-5.webp</t>
-  </si>
-  <si>
-    <t>IMG9</t>
-  </si>
-  <si>
-    <t>IMG10</t>
-  </si>
-  <si>
-    <t>IMG11</t>
-  </si>
-  <si>
-    <t>IMG12</t>
-  </si>
-  <si>
-    <t>IMG13</t>
-  </si>
-  <si>
-    <t>IMG14</t>
-  </si>
-  <si>
-    <t>IMG9,IMG10,IMG11,IMG12,IMG13,IMG14</t>
-  </si>
-  <si>
-    <t>https://xanhworld.vn/san-pham/cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung</t>
   </si>
   <si>
     <t>&lt;h2 style="color:#3bb77e; font-weight:700; margin-top:20px;"&gt;
@@ -1082,27 +629,1165 @@
   &lt;/blockquote&gt;
 &lt;/div&gt;</t>
   </si>
+  <si>
+    <t>Cây Lưỡi Hổ: Ý Nghĩa Phong Thủy, Công Dụng, Cách Chăm Sóc Chi Tiết</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ – loại cây phong thủy nổi bật với khả năng thanh lọc không khí, hút tài lộc và mang lại năng lượng tích cực. Tìm hiểu ý nghĩa, cách chăm sóc và công dụng chi tiết của cây Lưỡi Hổ.</t>
+  </si>
+  <si>
+    <t>cây lưỡi hổ,ý nghĩa cây lưỡi hổ,công dụng cây lưỡi hổ,chăm sóc cây lưỡi hổ,cây phong thủy trong nhà,cây hút tài lộc,cây lọc không khí,lưỡi hổ phong thủy,cây để bàn dễ chăm</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung</t>
+  </si>
+  <si>
+    <t>cây lưỡi hổ,cây phong thủy,cây lọc không khí,cây trong nhà,cây để bàn,tài lộc,bảo vệ sức khỏe</t>
+  </si>
+  <si>
+    <t>IMG19,IMG20,IMG21,IMG22,IMG13,IMG14</t>
+  </si>
+  <si>
+    <t>XWCLV071225</t>
+  </si>
+  <si>
+    <t>Cây Lộc Vừng: Đặc Điểm, Ý Nghĩa và Bảng Giá Cập Nhật</t>
+  </si>
+  <si>
+    <t>cay-loc-vung-dac-diem-y-nghia-va-bang-gia-cap-nhat</t>
+  </si>
+  <si>
+    <t>&lt;h2 style="color: #3bb77e; font-weight: bold; margin-top: 20px;"&gt;C&amp;Acirc;Y LỘC VỪNG &amp;ndash; C&amp;Acirc;Y C&amp;Ocirc;NG TR&amp;Igrave;NH B&amp;Oacute;NG M&amp;Aacute;T CAO CẤP VỚI GI&amp;Aacute; TRỊ CẢNH QUAN V&amp;Agrave; PHONG THỦY ĐẶC BIỆT&lt;/h2&gt;
+&lt;div style="line-height: 1.7; font-size: 16px;"&gt;
+&lt;p&gt;&lt;strong style="color: #3bb77e;"&gt;C&amp;acirc;y Lộc Vừng&lt;/strong&gt; (Barringtonia acutangula) l&amp;agrave; một trong những loại c&amp;acirc;y c&amp;ocirc;ng tr&amp;igrave;nh b&amp;oacute;ng m&amp;aacute;t được y&amp;ecirc;u th&amp;iacute;ch nhờ vẻ đẹp sang trọng, hoa đỏ rực rỡ v&amp;agrave; &amp;yacute; nghĩa phong thủy gắn liền với t&amp;agrave;i lộc &amp;ndash; may mắn. C&amp;acirc;y xuất hiện nhiều trong c&amp;aacute;c c&amp;ocirc;ng tr&amp;igrave;nh lớn như c&amp;ocirc;ng vi&amp;ecirc;n, khu đ&amp;ocirc; thị, khu sinh th&amp;aacute;i, resort, biệt thự v&amp;agrave; c&amp;aacute;c dự &amp;aacute;n cảnh quan quy m&amp;ocirc;. Với khả năng sinh trưởng mạnh, chịu hạn, chịu nhiệt v&amp;agrave; chống x&amp;oacute;i m&amp;ograve;n tốt, c&amp;acirc;y Lộc Vừng c&amp;ograve;n l&amp;agrave; lựa chọn h&amp;agrave;ng đầu cho c&amp;aacute;c khu vực ven biển, ven s&amp;ocirc;ng.&lt;/p&gt;
+&lt;p&gt;Kh&amp;ocirc;ng chỉ mang gi&amp;aacute; trị thẩm mỹ v&amp;agrave; phong thủy, c&amp;acirc;y Lộc Vừng c&amp;ograve;n l&amp;agrave; loại c&amp;acirc;y c&amp;oacute; tuổi thọ cao, gi&amp;aacute; trị kinh tế lớn. C&amp;acirc;y c&amp;agrave;ng gi&amp;agrave;, c&amp;agrave;ng đẹp, d&amp;aacute;ng c&amp;agrave;ng độc &amp;ndash; gi&amp;aacute; trị c&amp;agrave;ng tăng theo thời gian.&lt;/p&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;ĐẶC ĐIỂM CHI TIẾT CỦA C&amp;Acirc;Y LỘC VỪNG&lt;/h3&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;T&amp;ecirc;n khoa học:&lt;/strong&gt; Barringtonia acutangula&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;T&amp;ecirc;n gọi kh&amp;aacute;c:&lt;/strong&gt; C&amp;acirc;y Mưng, C&amp;acirc;y Chiếc&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Họ:&lt;/strong&gt; Lecythidaceae&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Nguồn gốc:&lt;/strong&gt; Nam &amp;Aacute;, Bắc &amp;Uacute;c &amp;ndash; ph&amp;acirc;n bố từ Afghanistan đến Philippines, Queensland&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Ph&amp;acirc;n bố tại Việt Nam:&lt;/strong&gt; C&amp;oacute; mặt tr&amp;ecirc;n khắp l&amp;atilde;nh thổ, từ Bắc v&amp;agrave;o Nam đến tận C&amp;ocirc;n Đảo&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Th&amp;acirc;n c&amp;acirc;y:&lt;/strong&gt; Gỗ chắc, sinh trưởng mạnh, ph&amp;acirc;n t&amp;aacute;n c&amp;agrave;nh tốt&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;T&amp;aacute;n l&amp;aacute;:&lt;/strong&gt; Rộng, xanh quanh năm, tạo b&amp;oacute;ng m&amp;aacute;t tự nhi&amp;ecirc;n&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;L&amp;aacute;:&lt;/strong&gt; H&amp;igrave;nh m&amp;aacute;c, mềm, b&amp;oacute;ng, nhiều nước&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Hoa:&lt;/strong&gt; Nở 2 đợt: th&amp;aacute;ng 4&amp;ndash;6 v&amp;agrave; 9&amp;ndash;11, m&amp;agrave;u đỏ rực hoặc trắng tinh khiết&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Ch&amp;ugrave;m hoa:&lt;/strong&gt; D&amp;agrave;i, rủ xuống tạo th&amp;agrave;nh dải hoa đẹp mắt&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Quả:&lt;/strong&gt; H&amp;igrave;nh hộp/tr&amp;ograve;n d&amp;agrave;i 9&amp;ndash;11cm, chuyển v&amp;agrave;ng n&amp;acirc;u khi ch&amp;iacute;n&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Tuổi thọ:&lt;/strong&gt; Rất l&amp;acirc;u năm, c&amp;agrave;ng gi&amp;agrave; c&amp;agrave;ng c&amp;oacute; gi&amp;aacute; trị nghệ thuật&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;ƯU ĐIỂM NỔI BẬT&lt;/h3&gt;
+&lt;ul&gt;
+&lt;li&gt;Hoa đỏ rực rỡ, nở đều đặn 2 lần/năm&lt;/li&gt;
+&lt;li&gt;T&amp;aacute;n l&amp;aacute; rộng &amp;ndash; tạo b&amp;oacute;ng m&amp;aacute;t xuất sắc&lt;/li&gt;
+&lt;li&gt;Th&amp;iacute;ch nghi tốt m&amp;ocirc;i trường ven biển, ngập mặn&lt;/li&gt;
+&lt;li&gt;Chịu hạn, chịu nhiệt, dễ chăm s&amp;oacute;c&lt;/li&gt;
+&lt;li&gt;&amp;Iacute;t s&amp;acirc;u bệnh, ph&amp;aacute;t triển bền vững&lt;/li&gt;
+&lt;li&gt;Giữ đất, chống x&amp;oacute;i m&amp;ograve;n hiệu quả&lt;/li&gt;
+&lt;li&gt;Lọc bụi, hấp thụ kh&amp;iacute; độc, cải thiện chất lượng kh&amp;ocirc;ng kh&amp;iacute;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;PH&amp;Acirc;N LOẠI C&amp;Acirc;Y LỘC VỪNG&lt;/h3&gt;
+&lt;h4 style="color: #3bb77e;"&gt;1. C&amp;acirc;y Lộc Vừng Hoa Đỏ &amp;ndash; Phổ biến nhất&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;Hoa đỏ rực rỡ, mang sắc may mắn&lt;/li&gt;
+&lt;li&gt;Nguồn gốc Nam &amp;Aacute;, Philippines&lt;/li&gt;
+&lt;li&gt;D&amp;ugrave;ng trang tr&amp;iacute; s&amp;acirc;n vườn, trước cửa nh&amp;agrave;, khu đ&amp;ocirc; thị&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h4 style="color: #3bb77e;"&gt;2. C&amp;acirc;y Lộc Vừng Hoa Trắng&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;T&amp;ecirc;n khoa học: Barringtonia racemosa&lt;/li&gt;
+&lt;li&gt;Hoa trắng pha hồng nhẹ &amp;ndash; thanh tao, trang nh&amp;atilde;&lt;/li&gt;
+&lt;li&gt;Th&amp;iacute;ch hợp lối đi, cảnh quan cần sự tinh tế&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h4 style="color: #3bb77e;"&gt;3. C&amp;acirc;y Rau Vừng (Lộc Vừng Ven Biển)&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;Sinh sống v&amp;ugrave;ng ngập mặn, ven biển miền Nam&lt;/li&gt;
+&lt;li&gt;Quả mọc trực tiếp từ th&amp;acirc;n &amp;ndash; kh&amp;aacute;c với hai loại tr&amp;ecirc;n&lt;/li&gt;
+&lt;li&gt;B&amp;oacute;ng m&amp;aacute;t tốt, giữ đất hiệu quả&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;&amp;Yacute; NGHĨA PHONG THỦY&lt;/h3&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;Thuộc bộ tứ:&lt;/strong&gt; Sanh &amp;ndash; Sung &amp;ndash; T&amp;ugrave;ng &amp;ndash; Lộc (c&amp;acirc;y đem lại may mắn)&lt;/li&gt;
+&lt;li&gt;Đại diện cho nh&amp;oacute;m Ph&amp;uacute;c &amp;ndash; Lộc &amp;ndash; Thọ&lt;/li&gt;
+&lt;li&gt;Lộc = T&amp;agrave;i lộc, tiền bạc&lt;/li&gt;
+&lt;li&gt;&amp;ldquo;Vừng" gợi nhắc c&amp;acirc;u &amp;ldquo;Vừng ơi mở cửa ra&amp;rdquo; &amp;ndash; đ&amp;oacute;n may mắn v&amp;agrave;o nh&amp;agrave;&lt;/li&gt;
+&lt;li&gt;Hoa đỏ: Hỷ sự, t&amp;agrave;i lộc, may mắn&lt;/li&gt;
+&lt;li&gt;Th&amp;acirc;n chắc khỏe: Sự bền vững, trường tồn&lt;/li&gt;
+&lt;li&gt;T&amp;aacute;n rộng: Gắn kết, h&amp;ograve;a thuận, sung t&amp;uacute;c&lt;/li&gt;
+&lt;li&gt;Xua đuổi t&amp;agrave; kh&amp;iacute;, thu h&amp;uacute;t năng lượng t&amp;iacute;ch cực&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;M&amp;agrave;u sắc hợp mệnh:&lt;/strong&gt; Xanh (Mộc), Đỏ (Hỏa)&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Hợp mệnh:&lt;/strong&gt; Mộc, Hỏa&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Hợp tuổi:&lt;/strong&gt; Mậu Ngọ 1978, T&amp;acirc;n Dậu 1981, Đinh M&amp;atilde;o 1987, Kỷ Tỵ 1989&amp;hellip;&lt;/p&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;GI&amp;Aacute; TRỊ TRONG ĐỜI SỐNG&lt;/h3&gt;
+&lt;h4 style="color: #3bb77e;"&gt;1. T&amp;ocirc; điểm cảnh quan&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;Ch&amp;ugrave;m hoa đỏ rực đẹp như r&amp;egrave;m thi&amp;ecirc;n nhi&amp;ecirc;n&lt;/li&gt;
+&lt;li&gt;Tạo kh&amp;ocirc;ng gian sang trọng, thơ mộng&lt;/li&gt;
+&lt;li&gt;Giảm nắng n&amp;oacute;ng, l&amp;agrave;m m&amp;aacute;t s&amp;acirc;n vườn&lt;/li&gt;
+&lt;li&gt;Ph&amp;ugrave; hợp: biệt thự, khu đ&amp;ocirc; thị, c&amp;ocirc;ng vi&amp;ecirc;n, resort&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h4 style="color: #3bb77e;"&gt;2. Bảo vệ m&amp;ocirc;i trường&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;Lộc Vừng lọc bụi tốt, hấp thụ kh&amp;iacute; độc&lt;/li&gt;
+&lt;li&gt;T&amp;aacute;n l&amp;aacute; d&amp;agrave;y gi&amp;uacute;p giảm nhiệt độ m&amp;ocirc;i trường&lt;/li&gt;
+&lt;li&gt;Hệ rễ giữ đất, chống sạt lở ven s&amp;ocirc;ng, ven biển&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h4 style="color: #3bb77e;"&gt;3. Gi&amp;aacute; trị kinh tế&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;C&amp;acirc;y l&amp;acirc;u năm, d&amp;aacute;ng đẹp c&amp;oacute; gi&amp;aacute; trị từ v&amp;agrave;i triệu đến h&amp;agrave;ng trăm triệu&lt;/li&gt;
+&lt;li&gt;Được ưa chuộng trong giới sưu tầm c&amp;acirc;y cảnh&lt;/li&gt;
+&lt;li&gt;D&amp;ugrave;ng tạo bonsai &amp;ndash; c&amp;agrave;ng l&amp;acirc;u năm c&amp;agrave;ng qu&amp;yacute;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h4 style="color: #3bb77e;"&gt;4. C&amp;ocirc;ng dụng y học&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;L&amp;aacute; v&amp;agrave; vỏ: giảm vi&amp;ecirc;m, trị nhiễm khuẩn&lt;/li&gt;
+&lt;li&gt;Rễ: hỗ trợ điều trị cao huyết &amp;aacute;p, đau nhức xương khớp&lt;/li&gt;
+&lt;li&gt;Dược liệu trong y học cổ truyền d&amp;acirc;n gian&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;BẢNG GI&amp;Aacute; SẢN PHẨM 2025&lt;/h3&gt;
+&lt;table style="border-collapse: collapse; width: 100%; border-color: #3bb77e;" border="1" cellspacing="0" cellpadding="10"&gt;
+&lt;tbody&gt;
+&lt;tr style="background: #3bb77e; color: white;"&gt;
+&lt;th&gt;Chiều cao c&amp;acirc;y&lt;/th&gt;
+&lt;th&gt;Size bầu&lt;/th&gt;
+&lt;th&gt;C&amp;ocirc;ng dụng&lt;/th&gt;
+&lt;th&gt;Gi&amp;aacute; (VNĐ)&lt;/th&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td&gt;50&amp;ndash;80cm&lt;/td&gt;
+&lt;td&gt;15&amp;ndash;20cm&lt;/td&gt;
+&lt;td&gt;C&amp;acirc;y giống, bonsai nhỏ&lt;/td&gt;
+&lt;td&gt;80.000 &amp;ndash; 120.000&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td&gt;80cm&amp;ndash;1,2m&lt;/td&gt;
+&lt;td&gt;20&amp;ndash;25cm&lt;/td&gt;
+&lt;td&gt;S&amp;acirc;n vườn nhỏ, chậu cảnh&lt;/td&gt;
+&lt;td&gt;150.000 &amp;ndash; 200.000&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td&gt;1,2&amp;ndash;1,5m&lt;/td&gt;
+&lt;td&gt;25&amp;ndash;30cm&lt;/td&gt;
+&lt;td&gt;Biệt thự, cảnh quan s&amp;acirc;n vườn&lt;/td&gt;
+&lt;td&gt;250.000 &amp;ndash; 350.000&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td&gt;1,5&amp;ndash;2m&lt;/td&gt;
+&lt;td&gt;30&amp;ndash;40cm&lt;/td&gt;
+&lt;td&gt;C&amp;ocirc;ng vi&amp;ecirc;n, khu đ&amp;ocirc; thị&lt;/td&gt;
+&lt;td&gt;450.000 &amp;ndash; 600.000&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td&gt;Tr&amp;ecirc;n 2m&lt;/td&gt;
+&lt;td&gt;40&amp;ndash;50cm&lt;/td&gt;
+&lt;td&gt;Dự &amp;aacute;n lớn, đường phố&lt;/td&gt;
+&lt;td&gt;&lt;strong&gt;Li&amp;ecirc;n hệ&lt;/strong&gt;&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td&gt;C&amp;acirc;y đại thụ&lt;/td&gt;
+&lt;td&gt;Theo y&amp;ecirc;u cầu&lt;/td&gt;
+&lt;td&gt;Dự &amp;aacute;n cao cấp&lt;/td&gt;
+&lt;td&gt;&lt;strong&gt;Li&amp;ecirc;n hệ&lt;/strong&gt;&lt;/td&gt;
+&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p style="font-style: italic; margin-top: 10px;"&gt;Gi&amp;aacute; tham khảo &amp;ndash; thay đổi t&amp;ugrave;y thời điểm, d&amp;aacute;ng c&amp;acirc;y v&amp;agrave; số lượng.&lt;/p&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;VỊ TR&amp;Iacute; TRỒNG PH&amp;Ugrave; HỢP&lt;/h3&gt;
+&lt;ul&gt;
+&lt;li&gt;S&amp;acirc;n vườn biệt thự, villa, resort&lt;/li&gt;
+&lt;li&gt;C&amp;ocirc;ng vi&amp;ecirc;n đ&amp;ocirc; thị, khu sinh hoạt cộng đồng&lt;/li&gt;
+&lt;li&gt;C&amp;acirc;y tuyến đường, dải ph&amp;acirc;n c&amp;aacute;ch&lt;/li&gt;
+&lt;li&gt;Trước nh&amp;agrave; &amp;ndash; tăng t&amp;agrave;i lộc&lt;/li&gt;
+&lt;li&gt;Qu&amp;aacute;n x&amp;aacute;, cửa h&amp;agrave;ng, khu kinh doanh&lt;/li&gt;
+&lt;li&gt;Khu sinh th&amp;aacute;i, dự &amp;aacute;n cảnh quan&lt;/li&gt;
+&lt;li&gt;V&amp;ugrave;ng ven biển &amp;ndash; chống x&amp;oacute;i m&amp;ograve;n&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;HƯỚNG DẪN TRỒNG C&amp;Acirc;Y&lt;/h3&gt;
+&lt;h4 style="color: #3bb77e;"&gt;Phương ph&amp;aacute;p chiết c&amp;agrave;nh (Khuyến nghị)&lt;/h4&gt;
+&lt;ol&gt;
+&lt;li&gt;Chuẩn bị dao sắc, đất tơi xốp, t&amp;uacute;i nilon, trấu, rễ b&amp;egrave;o&lt;/li&gt;
+&lt;li&gt;Khoanh vỏ c&amp;agrave;nh khỏe, b&amp;oacute; hỗn hợp đất &amp;ndash; trấu &amp;ndash; rễ b&amp;egrave;o&lt;/li&gt;
+&lt;li&gt;Bọc nilon giữ ẩm để rễ ph&amp;aacute;t triển&lt;/li&gt;
+&lt;li&gt;Cắt c&amp;agrave;nh chiết v&amp;agrave; trồng v&amp;agrave;o chậu/hố đất&lt;/li&gt;
+&lt;li&gt;Thời điểm tốt nhất: Th&amp;aacute;ng 6&amp;ndash;7&lt;/li&gt;
+&lt;/ol&gt;
+&lt;h4 style="color: #3bb77e;"&gt;Gieo hạt (&amp;iacute;t d&amp;ugrave;ng hơn)&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;Chọn hạt từ quả ch&amp;iacute;n&lt;/li&gt;
+&lt;li&gt;Gieo v&amp;agrave;o đất tơi, giữ ẩm&lt;/li&gt;
+&lt;li&gt;Ươm c&amp;acirc;y non cho đến khi đạt đủ chiều cao&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h4 style="color: #3bb77e;"&gt;Trồng ngo&amp;agrave;i vườn&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;Đ&amp;agrave;o hố s&amp;acirc;u vừa phải&lt;/li&gt;
+&lt;li&gt;Đặt c&amp;acirc;y, lấp đất, cố định th&amp;acirc;n&lt;/li&gt;
+&lt;li&gt;Tưới đều v&amp;agrave; che nắng nhẹ ban đầu&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h4 style="color: #3bb77e;"&gt;Trồng chậu&lt;/h4&gt;
+&lt;ul&gt;
+&lt;li&gt;D&amp;ugrave;ng chậu s&amp;acirc;u, rộng&lt;/li&gt;
+&lt;li&gt;Đất tơi, tho&amp;aacute;t nước tốt&lt;/li&gt;
+&lt;li&gt;Th&amp;iacute;ch hợp trồng bonsai hoặc c&amp;acirc;y cảnh nhỏ&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;HƯỚNG DẪN CHĂM S&amp;Oacute;C&lt;/h3&gt;
+&lt;p&gt;&lt;strong style="color: #3bb77e;"&gt;Đất trồng:&lt;/strong&gt; Đất tơi xốp, pha trấu, xơ dừa, ph&amp;acirc;n chuồng hoai.&lt;/p&gt;
+&lt;p&gt;&lt;strong style="color: #3bb77e;"&gt;Tưới nước:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;C&amp;acirc;y non: tưới 2 lần/ng&amp;agrave;y&lt;/li&gt;
+&lt;li&gt;C&amp;acirc;y lớn: tưới vừa đủ, tr&amp;aacute;nh ngập &amp;uacute;ng&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong style="color: #3bb77e;"&gt;&amp;Aacute;nh s&amp;aacute;ng:&lt;/strong&gt; Ưa s&amp;aacute;ng mạnh, cần nơi tho&amp;aacute;ng.&lt;/p&gt;
+&lt;p&gt;&lt;strong style="color: #3bb77e;"&gt;B&amp;oacute;n ph&amp;acirc;n:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;C&amp;acirc;y nhỏ: B&amp;oacute;n ph&amp;acirc;n định kỳ mỗi th&amp;aacute;ng&lt;/li&gt;
+&lt;li&gt;C&amp;acirc;y lớn: B&amp;oacute;n nhẹ&lt;/li&gt;
+&lt;li&gt;C&amp;acirc;y sắp ra hoa: Bổ sung ph&amp;acirc;n k&amp;iacute;ch th&amp;iacute;ch nụ&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong style="color: #3bb77e;"&gt;Nhiệt độ:&lt;/strong&gt; Th&amp;iacute;ch nghi tốt, chịu nắng n&amp;oacute;ng lẫn r&amp;eacute;t nhẹ.&lt;/p&gt;
+&lt;p&gt;&lt;strong style="color: #3bb77e;"&gt;Ph&amp;ograve;ng s&amp;acirc;u bệnh:&lt;/strong&gt; Kiểm tra l&amp;aacute;, tỉa c&amp;agrave;nh s&amp;acirc;u, d&amp;ugrave;ng biện ph&amp;aacute;p sinh học.&lt;/p&gt;
+&lt;p&gt;&lt;strong style="color: #3bb77e;"&gt;Chăm s&amp;oacute;c c&amp;acirc;y mới trồng:&lt;/strong&gt; Che nắng 5&amp;ndash;7 ng&amp;agrave;y đầu, tưới giữ ẩm.&lt;/p&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;LƯU &amp;Yacute; KHI CHỌN MUA C&amp;Acirc;Y&lt;/h3&gt;
+&lt;ul&gt;
+&lt;li&gt;L&amp;aacute; xanh, kh&amp;ocirc;ng v&amp;agrave;ng &amp;uacute;a&lt;/li&gt;
+&lt;li&gt;Th&amp;acirc;n thẳng, khỏe, kh&amp;ocirc;ng sẹo bệnh&lt;/li&gt;
+&lt;li&gt;Rễ trắng, chắc, kh&amp;ocirc;ng bị thối&lt;/li&gt;
+&lt;li&gt;K&amp;iacute;ch thước ph&amp;ugrave; hợp kh&amp;ocirc;ng gian dự &amp;aacute;n&lt;/li&gt;
+&lt;li&gt;Y&amp;ecirc;u cầu giấy chứng nhận nguồn gốc&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h3 style="color: #3bb77e; margin-top: 30px;"&gt;ƯU THẾ KHI CHỌN C&amp;Acirc;Y LỘC VỪNG TRONG CẢNH QUAN&lt;/h3&gt;
+&lt;p&gt;C&amp;acirc;y Lộc Vừng kh&amp;ocirc;ng chỉ tạo b&amp;oacute;ng m&amp;aacute;t m&amp;agrave; c&amp;ograve;n mang lại sự thịnh vượng, may mắn v&amp;agrave; vẻ đẹp sinh th&amp;aacute;i bền vững. T&amp;aacute;n l&amp;aacute; rộng, rễ khỏe v&amp;agrave; hoa rũ xuống thơ mộng khiến c&amp;acirc;y trở th&amp;agrave;nh điểm nhấn tuyệt đẹp trong mọi c&amp;ocirc;ng tr&amp;igrave;nh.&lt;/p&gt;
+&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Cây Lộc Vừng là lựa chọn lý tưởng cho sân vườn, công trình và khu đô thị nhờ tán rộng, hoa đẹp và sức sống mạnh. Nhận báo giá sỉ theo số lượng, hỗ trợ vận chuyển toàn quốc.</t>
+  </si>
+  <si>
+    <t>cây lộc vừng,cây công trình bóng mát,cây lộc vừng hoa đỏ,lộc vừng công trình,giá cây lộc vừng,cây bóng mát đô thị,cây cảnh quan,cây trồng biệt thự,cây lộc vừng giá sỉ</t>
+  </si>
+  <si>
+    <t>cay-canh</t>
+  </si>
+  <si>
+    <t>cay-canh,cay-ngoai-troi</t>
+  </si>
+  <si>
+    <t>cây lộc vừng,cây công trình,cây bóng mát,cây phong thủy,lộc vừng hoa đỏ,cây cảnh quan,cây trồng đô thị</t>
+  </si>
+  <si>
+    <t>IMG23</t>
+  </si>
+  <si>
+    <t>image_key</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>alt</t>
+  </si>
+  <si>
+    <t>is_primary</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>IMG1</t>
+  </si>
+  <si>
+    <t>cay-phat-tai-de-ban-gia-tot.webp</t>
+  </si>
+  <si>
+    <t>IMG2</t>
+  </si>
+  <si>
+    <t>cay-phat-tai-1.webp</t>
+  </si>
+  <si>
+    <t>IMG3</t>
+  </si>
+  <si>
+    <t>cay-phat-tai.webp</t>
+  </si>
+  <si>
+    <t>IMG4</t>
+  </si>
+  <si>
+    <t>cay-phat-tai-khuc-bo-3-nho.webp</t>
+  </si>
+  <si>
+    <t>IMG5</t>
+  </si>
+  <si>
+    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao.webp</t>
+  </si>
+  <si>
+    <t>IMG6</t>
+  </si>
+  <si>
+    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao-1.webp</t>
+  </si>
+  <si>
+    <t>IMG7</t>
+  </si>
+  <si>
+    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao-2.webp</t>
+  </si>
+  <si>
+    <t>IMG8</t>
+  </si>
+  <si>
+    <t>cay-kim-tien-y-nghia-phong-thuy-cach-cham-soc-gia-tham-khao-3.webp</t>
+  </si>
+  <si>
+    <t>IMG19</t>
+  </si>
+  <si>
+    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung.webp</t>
+  </si>
+  <si>
+    <t>IMG20</t>
+  </si>
+  <si>
+    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-1.webp</t>
+  </si>
+  <si>
+    <t>IMG21</t>
+  </si>
+  <si>
+    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-2.webp</t>
+  </si>
+  <si>
+    <t>IMG22</t>
+  </si>
+  <si>
+    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-3.webp</t>
+  </si>
+  <si>
+    <t>IMG13</t>
+  </si>
+  <si>
+    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-4.webp</t>
+  </si>
+  <si>
+    <t>IMG14</t>
+  </si>
+  <si>
+    <t>cay-luoi-ho-y-nghia-phong-thuy-cach-cham-soc-cong-dung-5.webp</t>
+  </si>
+  <si>
+    <t>cay-loc-vung-dac-diem-y-nghia-va-bang-gia-cap-nhat.png</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>Cây phát tài có ý nghĩa gì trong phong thủy?</t>
+  </si>
+  <si>
+    <t>Cây phát tài tượng trưng cho tài lộc, may mắn, vượng khí và sự thịnh vượng. Cây phù hợp đặt tại nhà ở, văn phòng, cửa hàng kinh doanh để thu hút năng lượng tích cực.</t>
+  </si>
+  <si>
+    <t>Cây phát tài hợp mệnh gì?</t>
+  </si>
+  <si>
+    <t>Tùy từng loại:
+Phát tài núi hợp mệnh Thủy – Mộc – Hỏa
+Phát lộc hợp mệnh Kim
+Phát tài đỏ hợp mệnh Hỏa
+Búp sen hợp mệnh Kim – Mộc – Thủy
+Hầu hết các loại đều phù hợp nhiều mệnh trong ngũ hành.</t>
+  </si>
+  <si>
+    <t>Cây phát tài chăm sóc có khó không?</t>
+  </si>
+  <si>
+    <t>Không. Cây rất dễ chăm: sống tốt trong môi trường thiếu sáng, chỉ cần tưới nước định kỳ và thỉnh thoảng tắm nắng nhẹ để cây xanh tốt.</t>
+  </si>
+  <si>
+    <t>Cây phát tài nên đặt ở vị trí nào?</t>
+  </si>
+  <si>
+    <t>Theo phong thủy, nên đặt ở hướng Đông hoặc Đông Nam để thu hút tài lộc. Trong thực tế có thể đặt ở bàn làm việc, phòng khách, quầy lễ tân, lối vào cửa hàng.</t>
+  </si>
+  <si>
+    <t>Bao lâu nên thay chậu cho cây phát tài?</t>
+  </si>
+  <si>
+    <t>Thông thường 1 năm thay chậu 1 lần để giúp bộ rễ phát triển khỏe, đất tơi xốp, thoát nước tốt hơn.</t>
+  </si>
+  <si>
+    <t>Cây phát tài có độc không?</t>
+  </si>
+  <si>
+    <t>Đa số các loại không độc. Một số ít có thể gây kích ứng nhẹ nếu nhựa cây dính vào da, chỉ cần rửa sạch sau khi cắt tỉa.</t>
+  </si>
+  <si>
+    <t>Cây phát tài giá bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Tùy loại và kích thước:
+Từ 70.000đ đến khoảng 3.000.000đ
+Giá cao hơn đối với cây lớn, lâu năm hoặc tạo dáng phong thủy.</t>
+  </si>
+  <si>
+    <t>Cây phát tài trồng thủy sinh được không?</t>
+  </si>
+  <si>
+    <t>Có. Một số loại như phát tài búp sen hoặc phát lộc rất phù hợp trồng thủy sinh, dễ chăm, sạch đẹp.</t>
+  </si>
+  <si>
+    <t>Cây phát tài ra hoa có ý nghĩa gì?</t>
+  </si>
+  <si>
+    <t>Cây phát tài ra hoa được xem là dấu hiệu tài lộc – vận may đang đến. Đây là hiện tượng hiếm gặp và được xem là điềm tốt.</t>
+  </si>
+  <si>
+    <t>Tôi mới bắt đầu chơi cây, có nên mua cây phát tài không?</t>
+  </si>
+  <si>
+    <t>Rất phù hợp. Cây dễ trồng, ít sâu bệnh, chăm sóc đơn giản và mang ý nghĩa phong thủy tốt, phù hợp cả người mới chơi.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền có ý nghĩa gì trong phong thủy?</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền tượng trưng cho tài lộc, may mắn, sự thịnh vượng và phát triển. Đây là loại cây được tin rằng mang đến nguồn năng lượng tích cực, giúp thu hút tiền bạc và vận khí tốt.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền hợp mệnh gì?</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền thuộc hành Mộc, rất hợp với người mệnh Mộc và Hỏa. Tuy nhiên hầu hết các mệnh khác vẫn có thể trồng vì cây mang tính trung hòa, dễ dung hòa với không gian sống.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền có dễ chăm sóc không?</t>
+  </si>
+  <si>
+    <t>Rất dễ. Cây chịu bóng tốt, sống khỏe trong môi trường máy lạnh, chỉ cần tưới nước vừa phải và giữ đất thoát nước tốt.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền nên đặt ở đâu để hút tài lộc?</t>
+  </si>
+  <si>
+    <t>Phong thủy khuyên đặt ở hướng Đông hoặc Đông Nam để kích hoạt tài lộc. Trong thực tế có thể đặt tại bàn làm việc, phòng khách, quầy lễ tân hoặc cửa hàng kinh doanh.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền bao lâu thì nên thay chậu?</t>
+  </si>
+  <si>
+    <t>Thường 1–2 năm thay chậu một lần vì bộ rễ của cây phát triển mạnh. Việc thay chậu giúp đất tơi xốp hơn và cây sinh trưởng tốt.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền có độc không?</t>
+  </si>
+  <si>
+    <t>Cây không độc nhưng nhựa cây có thể gây kích ứng nhẹ nếu dính vào da. Khi cắt tỉa chỉ cần rửa tay sạch là được.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền giá bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Tùy kích thước và dáng cây:_x000D_
+_x000D_
+15–30cm: 70.000đ – 100.000đ_x000D_
+30–50cm: 200.000đ – 350.000đ_x000D_
+Trên 50cm: 350.000đ – 500.000đ_x000D_
+_x000D_
+Giá thay đổi theo chậu, chất lượng rễ và dáng cây.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền có trồng thủy sinh được không?</t>
+  </si>
+  <si>
+    <t>Có. Cây Kim Tiền trồng thủy sinh rất đẹp, sạch và dễ chăm, chỉ cần thay nước định kỳ và đặt nơi có ánh sáng nhẹ.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền ra hoa có ý nghĩa gì?</t>
+  </si>
+  <si>
+    <t>Kim Tiền ra hoa được xem là điềm cực kỳ may mắn, báo hiệu tài lộc và cơ hội mới đang đến. Đây là hiện tượng hiếm gặp và mang ý nghĩa tốt lành.</t>
+  </si>
+  <si>
+    <t>Tại sao cây Kim Tiền bị vàng lá?</t>
+  </si>
+  <si>
+    <t>Nguyên nhân thường gặp: tưới quá nhiều nước, đất bí, thiếu ánh sáng, hoặc cây bị nấm rễ. Cần kiểm tra độ ẩm đất và điều chỉnh ánh sáng, đồng thời cắt bỏ lá vàng.</t>
+  </si>
+  <si>
+    <t>Cách tưới nước cho cây Kim Tiền thế nào là đúng?</t>
+  </si>
+  <si>
+    <t>Tưới 1–2 lần/tuần bằng cách phun sương khi đất còn ẩm. Không tưới quá nhiều vì cây chịu úng rất kém. Mỗi tháng có thể tưới đẫm một lần.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền có sống được trong phòng lạnh không?</t>
+  </si>
+  <si>
+    <t>Có. Cây sống rất tốt trong môi trường máy lạnh, văn phòng hoặc nơi ít ánh sáng.</t>
+  </si>
+  <si>
+    <t>Nên dùng đất gì để trồng cây Kim Tiền?</t>
+  </si>
+  <si>
+    <t>Dùng đất tơi xốp, thoát nước tốt như đất mùn, trộn thêm trấu hun, xơ dừa hoặc xỉ than giúp hạn chế úng rễ.</t>
+  </si>
+  <si>
+    <t>Bao lâu nên bón phân cho cây Kim Tiền?</t>
+  </si>
+  <si>
+    <t>2–3 tháng bón phân một lần. Dùng phân hữu cơ hoặc phân NPK dành cho cây cảnh, rải cách gốc khoảng 10–15cm.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền có cần ánh sáng không?</t>
+  </si>
+  <si>
+    <t>Có, nhưng chỉ cần ánh sáng gián tiếp. Tránh để dưới nắng gắt vì có thể khiến lá cháy mép.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền có hợp đặt ở quầy thu ngân không?</t>
+  </si>
+  <si>
+    <t>Rất hợp. Đây là vị trí giúp thu hút tài lộc theo quan niệm phong thủy, thường thấy ở cửa hàng, spa và doanh nghiệp.</t>
+  </si>
+  <si>
+    <t>Cây Kim Tiền có thể để trên bàn làm việc không?</t>
+  </si>
+  <si>
+    <t>Được. Kích thước nhỏ từ 15–30cm rất phù hợp đặt bàn, giúp mang đến cảm giác xanh mát và may mắn trong công việc.</t>
+  </si>
+  <si>
+    <t>Cách nhân giống cây Kim Tiền như thế nào?</t>
+  </si>
+  <si>
+    <t>Có thể nhân giống bằng cành hoặc bằng lá. Cắt lá hoặc cành khỏe, để khô vài giờ rồi cắm vào đất ẩm. Sau 1 tháng cây sẽ ra rễ mới.</t>
+  </si>
+  <si>
+    <t>Vì sao đất trồng cây Kim Tiền có mùi hoặc bị nấm?</t>
+  </si>
+  <si>
+    <t>Do tưới quá nhiều hoặc chậu không thoát nước tốt. Cần thay đất mới và giảm lượng nước tưới.</t>
+  </si>
+  <si>
+    <t>Người mới chơi cây có nên chọn cây Kim Tiền không?</t>
+  </si>
+  <si>
+    <t>Rất nên. Đây là loại cây dễ trồng nhất trong nhóm cây phong thủy, ít sâu bệnh, sống khỏe và mang nhiều ý nghĩa tốt lành.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ có ý nghĩa gì trong phong thủy?</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ tượng trưng cho sức mạnh, sự bảo vệ, xua đuổi năng lượng xấu và thu hút tài lộc. Là cây mang lại nguồn năng lượng dương mạnh mẽ cho không gian sống.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ hợp mệnh gì?</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ thuộc hành Mộc nhưng lại mang nét Kim do dáng lá sắc nhọn, vì vậy hợp với mệnh Kim, Mộc, Thổ.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ có lọc không khí không?</t>
+  </si>
+  <si>
+    <t>Có. Đây là một trong những loại cây được NASA công nhận có khả năng lọc khí độc như formaldehyde, benzene, toluene và biến CO₂ thành O₂ vào ban đêm.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ có dễ chăm không?</t>
+  </si>
+  <si>
+    <t>Rất dễ. Cây ưa khô, chịu hạn tốt, chỉ cần tưới 1 lần/tuần và đặt nơi có ánh sáng nhẹ.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ nên đặt ở đâu?</t>
+  </si>
+  <si>
+    <t>Có thể đặt ở phòng khách, phòng ngủ, văn phòng, cửa hàng hoặc nơi có nguồn khí không tốt để cân bằng năng lượng.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ có sống được trong phòng máy lạnh không?</t>
+  </si>
+  <si>
+    <t>Có. Cây sống tốt trong môi trường khô và ít sáng, rất phù hợp văn phòng.</t>
+  </si>
+  <si>
+    <t>Tưới nước cho cây Lưỡi Hổ thế nào là đúng?</t>
+  </si>
+  <si>
+    <t>Tưới 1 lần/7–10 ngày. Không tưới quá nhiều vì dễ gây úng rễ.</t>
+  </si>
+  <si>
+    <t>Tại sao lá Lưỡi Hổ bị nhăn hoặc mềm?</t>
+  </si>
+  <si>
+    <t>Do tưới quá nhiều hoặc đất bị nén chặt khiến rễ không thoáng khí. Cần thay đất hoặc giảm tưới.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ để phòng ngủ được không?</t>
+  </si>
+  <si>
+    <t>Được. Cây nhả oxy vào ban đêm, rất tốt cho đường hô hấp.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ có độc không?</t>
+  </si>
+  <si>
+    <t>Cây không độc nhưng nhựa của lá có thể gây kích ứng nhẹ khi nuốt hoặc tiếp xúc trực tiếp. Nên đặt xa trẻ nhỏ và thú cưng.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ giá bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Giá dao động từ 50.000đ đến 500.000đ tùy kích thước và số lượng bụi.</t>
+  </si>
+  <si>
+    <t>Bao lâu nên thay chậu cho cây Lưỡi Hổ?</t>
+  </si>
+  <si>
+    <t>1–2 năm thay chậu một lần để bộ rễ phát triển mạnh và đất tơi xốp hơn.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ có nhân giống được không?</t>
+  </si>
+  <si>
+    <t>Được. Có thể tách bụi hoặc cắt lá để nhân giống.</t>
+  </si>
+  <si>
+    <t>Vì sao lá Lưỡi Hổ bị cháy mép?</t>
+  </si>
+  <si>
+    <t>Do ánh nắng gắt chiếu trực tiếp hoặc thiếu nước trong thời gian dài.</t>
+  </si>
+  <si>
+    <t>Cây Lưỡi Hổ có đặt ở bàn làm việc được không?</t>
+  </si>
+  <si>
+    <t>Hoàn toàn được. Đây là cây phong thủy giúp tăng sự tập trung và xua đuổi khí xấu.</t>
+  </si>
+  <si>
+    <t>steps</t>
+  </si>
+  <si>
+    <t>supplies</t>
+  </si>
+  <si>
+    <t>Cách chăm sóc cây Phát Tài để cây luôn xanh tốt và thu hút tài lộc</t>
+  </si>
+  <si>
+    <t>Hướng dẫn các bước chăm sóc cây Phát Tài đúng cách để cây phát triển khỏe, lá xanh đẹp và mang lại năng lượng phong thủy tích cực cho ngôi nhà bạn.</t>
+  </si>
+  <si>
+    <t>["Bước 1: Đặt cây ở vị trí có ánh sáng nhẹ, tránh nắng gắt trực tiếp.","Bước 2: Tưới nước giữ ẩm vừa phải, không để đất bị úng.","Bước 3: Phun sương lên lá 2–3 lần mỗi tuần để cây quang hợp tốt.","Bước 4: Bón phân hữu cơ hoặc NPK loãng mỗi 1–2 tháng.","Bước 5: Tỉa bỏ lá vàng, thay chậu định kỳ 1 năm\/lần để cây phát triển khỏe."]</t>
+  </si>
+  <si>
+    <t>["Dụng cụ 1: Bình tưới nước hoặc bình phun sương","Dụng cụ 2: Phân bón hữu cơ hoặc NPK","Dụng cụ 3: Kéo cắt tỉa lá","Dụng cụ 4: Đất trồng tơi xốp, thoát nước tốt (nếu thay chậu)"]</t>
+  </si>
+  <si>
+    <t>Cách chăm sóc cây Kim Tiền để cây luôn xanh mướt và hút tài lộc</t>
+  </si>
+  <si>
+    <t>Hướng dẫn các bước chăm sóc cây Kim Tiền đúng cách để cây phát triển khỏe mạnh, lá bóng đẹp và mang lại tài lộc – may mắn cho không gian sống.</t>
+  </si>
+  <si>
+    <t>["Bước 1: Đặt cây ở nơi có ánh sáng gián tiếp, tránh nắng gắt chiếu trực tiếp vào lá.","Bước 2: Tưới nước 1–2 lần\/tuần bằng cách phun sương, chỉ tưới thêm khi đất khô bề mặt.","Bước 3: Duy trì độ thoáng cho đất, tránh để cây bị úng rễ bằng cách dùng chậu thoát nước tốt.","Bước 4: Bón phân hữu cơ hoặc phân chậm tan 2–3 tháng\/lần để cây phát triển ổn định.","Bước 5: Lau sạch lá mỗi tuần và cắt bỏ lá vàng để hạn chế sâu bệnh và giữ cây xanh đẹp.","Bước 6: Thay chậu định kỳ 1–2 năm\/lần giúp bộ rễ phát triển mạnh hơn."]</t>
+  </si>
+  <si>
+    <t>["Dụng cụ 1: Bình phun sương hoặc bình tưới","Dụng cụ 2: Đất trồng tơi xốp, thoát nước tốt","Dụng cụ 3: Phân hữu cơ hoặc phân NPK chậm tan","Dụng cụ 4: Khăn mềm để lau lá","Dụng cụ 5: Kéo cắt tỉa"]</t>
+  </si>
+  <si>
+    <t>Cách chăm sóc cây Lưỡi Hổ để cây luôn khỏe mạnh và lọc không khí tốt</t>
+  </si>
+  <si>
+    <t>Hướng dẫn các bước chăm sóc cây Lưỡi Hổ đúng kỹ thuật để cây sinh trưởng mạnh, lá cứng đẹp và phát huy tối đa khả năng thanh lọc không khí.</t>
+  </si>
+  <si>
+    <t>["Bước 1: Đặt cây ở nơi có ánh sáng nhẹ hoặc ánh sáng gián tiếp.","Bước 2: Tưới nước 7–10 ngày\/lần, chỉ tưới khi đất khô hoàn toàn.","Bước 3: Sử dụng đất tơi xốp, thoát nước tốt để tránh úng rễ.","Bước 4: Lau lá 1 lần\/tuần giúp cây quang hợp hiệu quả.","Bước 5: Bón phân hữu cơ hoặc phân tan chậm mỗi 2–3 tháng.","Bước 6: Thay chậu định kỳ 1–2 năm\/lần khi cây mọc nhiều bụi."]</t>
+  </si>
+  <si>
+    <t>["Dụng cụ 1: Bình tưới hoặc bình phun sương","Dụng cụ 2: Đất tơi xốp – thoát nước tốt","Dụng cụ 3: Phân hữu cơ hoặc phân tan chậm","Dụng cụ 4: Khăn mềm để lau lá","Dụng cụ 5: Kéo cắt tỉa hoặc dụng cụ tách bụi"]</t>
+  </si>
+  <si>
+    <t>product_sku</t>
+  </si>
+  <si>
+    <t>variant_name</t>
+  </si>
+  <si>
+    <t>variant_sku</t>
+  </si>
+  <si>
+    <t>image_id</t>
+  </si>
+  <si>
+    <t>attributes_json</t>
+  </si>
+  <si>
+    <t>sort_order</t>
+  </si>
+  <si>
+    <t>Cây Hồng Môn Đỏ Phong Thủy– Bán Lẻ, Bán Sỉ | Giá Ưu Đãi</t>
+  </si>
+  <si>
+    <t>Cây Vạn Lộc Để Bàn Phong Thủy – Giá Tốt, Dễ Chăm Sóc</t>
+  </si>
+  <si>
+    <t>Cây Trầu Bà Đế Vương Để Bàn &amp; Văn Phòng | Giao Cây Tận Nơi</t>
+  </si>
+  <si>
+    <t>Cây Giữ Tiền Phong Thủy Hợp Mệnh | Giá Tốt – Dễ Chăm</t>
+  </si>
+  <si>
+    <t>Cây Phú Quý Hợp Mệnh Kim – Giá Tốt, Dễ Chăm Sóc</t>
+  </si>
+  <si>
+    <t>Cây Giữ Tiền Thái Phong Thủy Giá Tốt | Thu Hút &amp; Giữ Tài Lộc</t>
+  </si>
+  <si>
+    <t>Cây Vạn Lộc 2 Thân Hợp Mệnh Kim, Hỏa | Giá Bán Hôm Nay</t>
+  </si>
+  <si>
+    <t>Cây Kim Ngân Hợp Mệnh Kim, Mộc | Giá Bán Hôm Nay</t>
+  </si>
+  <si>
+    <t>Cây Bạch Mã Hoàng Tử Phong Thủy Giá Tốt | Sang Trọng – Dễ Chăm</t>
+  </si>
+  <si>
+    <t>Cây Ngọc Ngân Phong Thủy Giá Tốt | Thanh Lọc Không Khí – Dễ Chăm</t>
+  </si>
+  <si>
+    <t>Cây Đinh Lăng Các Loại Cao 15–30cm | Cây Giống Khỏe – Giá Tốt</t>
+  </si>
+  <si>
+    <t>Cây Đinh Lăng Thái Lá Nhuyễn – Trồng Cảnh &amp; Làm Dược Liệu</t>
+  </si>
+  <si>
+    <t>Đinh Lăng Cẩm Thạch Mini | Cây Mini Trang Trí – Giá Tốt</t>
+  </si>
+  <si>
+    <t>Trúc Mini Làm Tiểu Cảnh | Cây Trang Trí Nhỏ Gọn – Giá Tốt</t>
+  </si>
+  <si>
+    <t>Cây Tùng La Hán Phong Thủy | Bán Cây Tùng Cảnh Giá Tốt</t>
+  </si>
+  <si>
+    <t>Mua Cây Cau Tiểu Trâm 1 Thân – Trang Trí Nhà &amp; Văn Phòng</t>
+  </si>
+  <si>
+    <t>Cây Trầu Bà Đế Vương Xanh Để Bàn | Dễ Chăm, Hợp Văn Phòng</t>
+  </si>
+  <si>
+    <t>Cây Trầu Bà Tỷ Phú | Trồng Thủy Sinh – Dễ Sống, Giá Tốt</t>
+  </si>
+  <si>
+    <t>Cẩm Tú Mai Thái (Sứ Thái Lan) | Cây Hoa Cảnh Đẹp, Dễ Chăm</t>
+  </si>
+  <si>
+    <t>Hoa Mười Giờ Sam Thái | Cây Hoa Nắng Đẹp, Dễ Trồng</t>
+  </si>
+  <si>
+    <t>Cây Phong Lá Đỏ Để Bàn – Giá Tốt, Cây Khỏe</t>
+  </si>
+  <si>
+    <t>Cây Hồng Môn phong thủy để bàn, hoa đẹp lâu tàn, mang ý nghĩa may mắn – tài lộc. Giá bán tốt, nhiều kích thước, giao cây tận nơi, bảo hành cây khỏe.</t>
+  </si>
+  <si>
+    <t>Cây Vạn Lộc phong thủy để bàn, lá đỏ hồng đẹp, tượng trưng tài lộc – may mắn. Giá bán tốt, nhiều kích thước, giao cây tận nơi, bảo hành cây khỏe.</t>
+  </si>
+  <si>
+    <t>Cây Trầu Bà Đế Vương phong thủy, biểu tượng quyền lực – tài lộc. Có nhiều kích thước, màu lá xanh/đỏ/vàng, giá tốt, giao cây tận nơi, bảo hành cây khỏe.</t>
+  </si>
+  <si>
+    <t>Cây Giữ Tiền phong thủy mang ý nghĩa giữ tài – hút lộc. Phù hợp để bàn, quầy thu ngân, văn phòng. Có sẵn nhiều kích thước, giá tốt, giao cây tận nơi.</t>
+  </si>
+  <si>
+    <t>Cây Phú Quý phong thủy tượng trưng cho giàu sang, may mắn. Phù hợp đặt bàn làm việc, phòng khách, quầy thu ngân. Có sẵn nhiều mẫu, giao cây tận nơi.</t>
+  </si>
+  <si>
+    <t>Cây Giữ Tiền Thái mang ý nghĩa giữ của – hút tài lộc, phù hợp đặt bàn làm việc, quầy thu ngân, cửa hàng kinh doanh. Có sẵn nhiều mẫu, giao cây tận nơi.</t>
+  </si>
+  <si>
+    <t>Cây Vạn Lộc 2 thân mang ý nghĩa tài lộc, song hỷ, thích hợp đặt bàn làm việc, quầy lễ tân, cửa hàng. Cây khỏe, dễ chăm sóc, giao tận nơi.</t>
+  </si>
+  <si>
+    <t>Cây Kim Ngân mang ý nghĩa tiền tài, thịnh vượng, thích hợp đặt bàn làm việc, phòng khách, quầy lễ tân. Cây khỏe, dễ chăm sóc, giao tận nơi.</t>
+  </si>
+  <si>
+    <t>Cây Bạch Mã Hoàng Tử mang ý nghĩa thăng tiến, thành công, thích hợp đặt bàn làm việc, phòng khách, văn phòng. Cây khỏe, lá đẹp, giao tận nơi.</t>
+  </si>
+  <si>
+    <t>Cây Ngọc Ngân mang ý nghĩa may mắn, tài lộc, thích hợp đặt bàn làm việc, phòng khách, văn phòng. Cây khỏe, lá đẹp, giao tận nơi.</t>
+  </si>
+  <si>
+    <t>Bán cây Đinh Lăng các loại cao 15–30cm, cây giống khỏe mạnh, dễ trồng, thích hợp làm thuốc, trồng vườn hoặc chậu. Giá tốt – giao nhanh.</t>
+  </si>
+  <si>
+    <t>Bán cây Đinh Lăng Thái lá nhuyễn, cây giống khỏe mạnh, lá mịn đẹp, dễ trồng, thích hợp trồng chậu hoặc đất vườn. Giá tốt – giao nhanh.</t>
+  </si>
+  <si>
+    <t>Bán cây Đinh lăng cẩm thạch mini, lá xanh viền trắng đẹp, cây nhỏ gọn, dễ chăm sóc, phù hợp để bàn, decor không gian. Giá tốt – giao nhanh.</t>
+  </si>
+  <si>
+    <t>Bán trúc mini làm tiểu cảnh, cây nhỏ gọn, xanh mát, dễ trồng, thích hợp trang trí tiểu cảnh, hòn non bộ, chậu cảnh mini. Giá tốt – giao nhanh.</t>
+  </si>
+  <si>
+    <t>Bán cây tùng la hán phong thủy, dáng đẹp, xanh bền, tượng trưng trường thọ – tài lộc. Phù hợp trồng sân vườn, biệt thự, tiểu cảnh. Giao cây tận nơi.</t>
+  </si>
+  <si>
+    <t>Bán cau tiểu trâm 1 thân dáng đẹp, lá xanh mướt, mang ý nghĩa may mắn – tài lộc. Phù hợp để bàn, phòng khách, văn phòng. Giao cây tận nơi.</t>
+  </si>
+  <si>
+    <t>Bán cây trầu bà đế vương xanh lá to, dáng đẹp, mang ý nghĩa quyền lực – tài lộc. Phù hợp để bàn làm việc, phòng khách, văn phòng. Giao cây tận nơi.</t>
+  </si>
+  <si>
+    <t>Cung cấp cây giống trầu bà tỷ phú trồng thủy sinh, cây khỏe, dễ sống, mang ý nghĩa tài lộc – may mắn. Phù hợp để bàn làm việc, văn phòng, nhà ở.</t>
+  </si>
+  <si>
+    <t>Bán cây cẩm tú mai Thái (sứ Thái Lan) hoa lớn, nhiều cánh, dáng đẹp. Phù hợp trồng chậu, sân vườn, ban công. Cây khỏe, dễ chăm sóc.</t>
+  </si>
+  <si>
+    <t>Hoa mười giờ sam Thái hoa to, nhiều cánh, nở rực dưới nắng. Phù hợp trồng chậu, bồn hoa, ban công. Cây dễ trồng, ít chăm sóc.</t>
+  </si>
+  <si>
+    <t>Cây phong lá đỏ (trầu bà lá đỏ) lá hồng đỏ nổi bật, dễ chăm sóc. Phù hợp trồng chậu, để bàn, phòng khách hoặc văn phòng.</t>
+  </si>
+  <si>
+    <t>cay-hong-mon-o-phong-thuy-ban-le-ban-si-gia-uu-ai</t>
+  </si>
+  <si>
+    <t>cay-van-loc-e-ban-phong-thuy-gia-tot-de-cham-soc</t>
+  </si>
+  <si>
+    <t>cay-trau-ba-e-vuong-e-ban-van-phong-giao-cay-tan-noi</t>
+  </si>
+  <si>
+    <t>cay-giu-tien-phong-thuy-hop-menh-gia-tot-de-cham</t>
+  </si>
+  <si>
+    <t>cay-phu-quy-hop-menh-kim-gia-tot-de-cham-soc</t>
+  </si>
+  <si>
+    <t>cay-giu-tien-thai-phong-thuy-gia-tot-thu-hut-giu-tai-loc</t>
+  </si>
+  <si>
+    <t>cay-van-loc-2-than-hop-menh-kim-hoa-gia-ban-hom-nay</t>
+  </si>
+  <si>
+    <t>cay-kim-ngan-hop-menh-kim-moc-gia-ban-hom-nay</t>
+  </si>
+  <si>
+    <t>cay-bach-ma-hoang-tu-phong-thuy-gia-tot-sang-trong-de-cham</t>
+  </si>
+  <si>
+    <t>cay-ngoc-ngan-phong-thuy-gia-tot-thanh-loc-khong-khi-de-cham</t>
+  </si>
+  <si>
+    <t>cay-inh-lang-cac-loai-cao-15-30cm-cay-giong-khoe-gia-tot</t>
+  </si>
+  <si>
+    <t>cay-inh-lang-thai-la-nhuyen-trong-canh-lam-duoc-lieu</t>
+  </si>
+  <si>
+    <t>truc-mini-lam-tieu-canh-cay-trang-tri-nho-gon-gia-tot</t>
+  </si>
+  <si>
+    <t>cay-tung-la-han-phong-thuy-ban-cay-tung-canh-gia-tot</t>
+  </si>
+  <si>
+    <t>mua-cay-cau-tieu-tram-1-than-trang-tri-nha-van-phong</t>
+  </si>
+  <si>
+    <t>cay-trau-ba-e-vuong-xanh-e-ban-de-cham-hop-van-phong</t>
+  </si>
+  <si>
+    <t>cay-trau-ba-ty-phu-trong-thuy-sinh-de-song-gia-tot</t>
+  </si>
+  <si>
+    <t>cam-tu-mai-thai-su-thai-lan-cay-hoa-canh-ep-de-cham</t>
+  </si>
+  <si>
+    <t>hoa-muoi-gio-sam-thai-cay-hoa-nang-ep-de-trong</t>
+  </si>
+  <si>
+    <t>cay-phong-la-o-e-ban-gia-tot-cay-khoe</t>
+  </si>
+  <si>
+    <t>XWCHMD1525</t>
+  </si>
+  <si>
+    <t>XWCVD1525</t>
+  </si>
+  <si>
+    <t>XWCTBD1525</t>
+  </si>
+  <si>
+    <t>XWCGTD1525</t>
+  </si>
+  <si>
+    <t>XWCBMD1525</t>
+  </si>
+  <si>
+    <t>XWCNND1525</t>
+  </si>
+  <si>
+    <t>XWCTD1525</t>
+  </si>
+  <si>
+    <t>XWCTMD1525</t>
+  </si>
+  <si>
+    <t>XWCDLT1525</t>
+  </si>
+  <si>
+    <t>XWCDLCL1525</t>
+  </si>
+  <si>
+    <t>XWĐDCT1525</t>
+  </si>
+  <si>
+    <t>XWTMNTC1525</t>
+  </si>
+  <si>
+    <t>XWCTLH1525</t>
+  </si>
+  <si>
+    <t>XWCCTT1525</t>
+  </si>
+  <si>
+    <t>XWH10HST1525</t>
+  </si>
+  <si>
+    <t>XWCPLD1525</t>
+  </si>
+  <si>
+    <t>XWCGT1525</t>
+  </si>
+  <si>
+    <t>XWCPQ1525</t>
+  </si>
+  <si>
+    <t>XWCVL2T1525</t>
+  </si>
+  <si>
+    <t>XWCKN1525</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-loc-vung-dac-diem-y-nghia-va-bang-gia-cap-nhat</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-hong-mon-o-phong-thuy-ban-le-ban-si-gia-uu-ai</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-van-loc-e-ban-phong-thuy-gia-tot-de-cham-soc</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-trau-ba-e-vuong-e-ban-van-phong-giao-cay-tan-noi</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-giu-tien-phong-thuy-hop-menh-gia-tot-de-cham</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-phu-quy-hop-menh-kim-gia-tot-de-cham-soc</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-giu-tien-thai-phong-thuy-gia-tot-thu-hut-giu-tai-loc</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-van-loc-2-than-hop-menh-kim-hoa-gia-ban-hom-nay</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-kim-ngan-hop-menh-kim-moc-gia-ban-hom-nay</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-bach-ma-hoang-tu-phong-thuy-gia-tot-sang-trong-de-cham</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-ngoc-ngan-phong-thuy-gia-tot-thanh-loc-khong-khi-de-cham</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/truc-mini-lam-tieu-canh-cay-trang-tri-nho-gon-gia-tot</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-tung-la-han-phong-thuy-ban-cay-tung-canh-gia-tot</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/mua-cay-cau-tieu-tram-1-than-trang-tri-nha-van-phong</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-trau-ba-e-vuong-xanh-e-ban-de-cham-hop-van-phong</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cam-tu-mai-thai-su-thai-lan-cay-hoa-canh-ep-de-cham</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/hoa-muoi-gio-sam-thai-cay-hoa-nang-ep-de-trong</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-phong-la-o-e-ban-gia-tot-cay-khoe</t>
+  </si>
+  <si>
+    <t>dinh-lang-cam-thach-mini-cay-mini-trang-tri-gia-tot</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-dinh-lang-cac-loai-cao-15-30cm-cay-giong-khoe-gia-tot</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-dinh-lang-thai-la-nhuyen-trong-canh-lam-duoc-lieu</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/cay-trau-ba-ty-phu-trong-thuy-sdinh-de-song-gia-tot</t>
+  </si>
+  <si>
+    <t>https://xanhworld.vn/san-pham/dinh-lang-cam-thach-mini-cay-mini-trang-tri-gia-tot</t>
+  </si>
+  <si>
+    <t>Cây hồng môn đỏ, cây hồng môn phong thủy, cây hồng môn để bàn, cây hồng môn trang trí, cây hồng môn bán sỉ, cây hồng môn bán lẻ, cây hồng môn giá ưu đãi</t>
+  </si>
+  <si>
+    <t>Cây hồng môn đỏ, cây hồng môn phong thủy, cây hồng môn đỏ phong thủy, cây hồng môn để bàn, cây hồng môn trang trí, cây hồng môn nội thất, cây phong thủy để bàn, cây cảnh phong thủy, cây cảnh văn phòng, cây cảnh để bàn làm việc, cây hồng môn bán lẻ, cây hồng môn bán sỉ, cây hồng môn giá rẻ, cây hồng môn giá ưu đãi, mua cây hồng môn, bán cây hồng môn, cây hồng môn đỏ đẹp, cây hồng môn hợp mệnh, cây hồng môn trang trí nhà</t>
+  </si>
+  <si>
+    <t>cây vạn lộc, cây vạn lộc để bàn, cây vạn lộc phong thủy, cây vạn lộc dễ chăm sóc, cây vạn lộc giá tốt, cây vạn lộc trang trí, cây cảnh để bàn, cây cảnh phong thủy, cây cảnh văn phòng, cây để bàn làm việc, cây cảnh nội thất, cây phong thủy để bàn</t>
+  </si>
+  <si>
+    <t>cây trầu bà đế vương, trầu bà đế vương để bàn, cây trầu bà đế vương văn phòng, cây trầu bà phong thủy</t>
+  </si>
+  <si>
+    <t>cây trầu bà đế vương, trầu bà đế vương để bàn, trầu bà đế vương văn phòng, cây trầu bà phong thủy, cây trầu bà trang trí, cây cảnh để bàn, cây cảnh văn phòng, cây phong thủy để bàn, cây nội thất xanh, cây xanh văn phòng, cây để bàn làm việc, giao cây tận nơi</t>
+  </si>
+  <si>
+    <t>cây giữ tiền phong thủy, cây giữ tiền hợp mệnh, cây giữ tiền dễ chăm, cây giữ tiền giá tốt</t>
+  </si>
+  <si>
+    <t>cây giữ tiền, cây giữ tiền phong thủy, cây giữ tiền hợp mệnh, cây giữ tiền để bàn, cây giữ tiền dễ chăm sóc, cây giữ tiền giá tốt, cây phong thủy để bàn, cây cảnh phong thủy, cây cảnh văn phòng, cây để bàn làm việc, cây nội thất xanh</t>
+  </si>
+  <si>
+    <t>cây phú quý hợp mệnh kim, cây phú quý phong thủy, cây phú quý dễ chăm sóc, cây phú quý giá tốt</t>
+  </si>
+  <si>
+    <t>cây phú quý, cây phú quý hợp mệnh kim, cây phú quý phong thủy, cây phú quý để bàn, cây phú quý dễ chăm sóc, cây phú quý giá tốt, cây phong thủy mệnh kim, cây cảnh phong thủy, cây cảnh để bàn, cây cảnh văn phòng, cây nội thất xanh</t>
+  </si>
+  <si>
+    <t>cây giữ tiền thái, cây giữ tiền thái phong thủy, cây giữ tiền thái giá tốt, cây giữ tiền thái tài lộc</t>
+  </si>
+  <si>
+    <t>cây giữ tiền thái, cây giữ tiền thái phong thủy, cây giữ tiền thái tài lộc, cây giữ tiền thái để bàn, cây giữ tiền thu hút tài lộc, cây phong thủy để bàn, cây cảnh phong thủy, cây cảnh văn phòng, cây để bàn làm việc, cây nội thất xanh</t>
+  </si>
+  <si>
+    <t>cây vạn lộc 2 thân, cây vạn lộc hợp mệnh kim hỏa, cây vạn lộc phong thủy, cây vạn lộc giá bán hôm nay</t>
+  </si>
+  <si>
+    <t>cây vạn lộc 2 thân, cây vạn lộc hợp mệnh kim, cây vạn lộc hợp mệnh hỏa, cây vạn lộc phong thủy, cây vạn lộc để bàn, cây vạn lộc trang trí, cây cảnh phong thủy, cây cảnh để bàn, cây cảnh văn phòng, cây nội thất xanh</t>
+  </si>
+  <si>
+    <t>cây kim ngân hợp mệnh kim mộc, cây kim ngân phong thủy, cây kim ngân giá bán hôm nay, cây kim ngân để bàn</t>
+  </si>
+  <si>
+    <t>cây kim ngân, cây kim ngân hợp mệnh kim, cây kim ngân hợp mệnh mộc, cây kim ngân phong thủy, cây kim ngân để bàn, cây kim ngân trang trí, cây phong thủy để bàn, cây cảnh phong thủy, cây cảnh văn phòng, cây nội thất xanh</t>
+  </si>
+  <si>
+    <t>cây bạch mã hoàng tử, cây bạch mã hoàng tử phong thủy, cây bạch mã hoàng tử giá tốt, cây bạch mã hoàng tử dễ chăm</t>
+  </si>
+  <si>
+    <t>cây bạch mã hoàng tử, cây bạch mã hoàng tử phong thủy, cây bạch mã hoàng tử để bàn, cây bạch mã hoàng tử văn phòng, cây bạch mã hoàng tử sang trọng, cây cảnh phong thủy, cây cảnh để bàn, cây cảnh văn phòng, cây nội thất xanh</t>
+  </si>
+  <si>
+    <t>cây ngọc ngân, cây ngọc ngân phong thủy, cây ngọc ngân giá tốt, cây ngọc ngân dễ chăm</t>
+  </si>
+  <si>
+    <t>cây ngọc ngân, cây ngọc ngân phong thủy, cây ngọc ngân để bàn, cây ngọc ngân thanh lọc không khí, cây ngọc ngân dễ chăm sóc, cây ngọc ngân trang trí, cây cảnh phong thủy, cây cảnh để bàn, cây cảnh văn phòng, cây nội thất xanh</t>
+  </si>
+  <si>
+    <t>cây đinh lăng, cây đinh lăng giống, cây đinh lăng cao 15–30cm, cây đinh lăng giá tốt</t>
+  </si>
+  <si>
+    <t>cây đinh lăng, cây đinh lăng giống, cây đinh lăng các loại, cây đinh lăng cao 15–30cm, cây giống đinh lăng, cây đinh lăng khỏe, cây đinh lăng để trồng, cây cảnh giống, cây dược liệu đinh lăng, cây giống giá tốt</t>
+  </si>
+  <si>
+    <t>cây đinh lăng thái lá nhuyễn, đinh lăng thái, cây đinh lăng làm dược liệu, cây đinh lăng trồng cảnh</t>
+  </si>
+  <si>
+    <t>cây đinh lăng thái, cây đinh lăng thái lá nhuyễn, đinh lăng thái, cây đinh lăng làm dược liệu, cây đinh lăng trồng cảnh, cây đinh lăng giống, cây dược liệu, cây cảnh lá nhuyễn, cây giống khỏe, cây giống giá tốt</t>
+  </si>
+  <si>
+    <t>đinh lăng cẩm thạch mini, cây đinh lăng cẩm thạch, cây đinh lăng mini trang trí, đinh lăng cẩm thạch giá tốt</t>
+  </si>
+  <si>
+    <t>đinh lăng cẩm thạch, đinh lăng cẩm thạch mini, cây đinh lăng cẩm thạch, cây đinh lăng mini, cây mini trang trí, cây cảnh để bàn, cây cảnh mini, cây trang trí nội thất, cây giống giá tốt</t>
+  </si>
+  <si>
+    <t>trúc mini, trúc mini tiểu cảnh, cây trúc mini trang trí, trúc mini giá tốt</t>
+  </si>
+  <si>
+    <t>trúc mini, cây trúc mini, trúc mini làm tiểu cảnh, cây trúc tiểu cảnh, cây mini trang trí, cây trang trí nhỏ gọn, cây cảnh mini, cây cảnh để bàn, cây nội thất xanh, cây trang trí giá tốt</t>
+  </si>
+  <si>
+    <t>cây tùng la hán, cây tùng la hán phong thủy, cây tùng cảnh, cây tùng la hán giá tốt</t>
+  </si>
+  <si>
+    <t>cây tùng la hán, tùng la hán phong thủy, cây tùng cảnh, cây tùng bonsai, cây tùng trang trí, cây cảnh phong thủy, cây cảnh sân vườn, cây cảnh nội thất, cây phong thủy tài lộc, bán cây tùng giá tốt</t>
+  </si>
+  <si>
+    <t>cây cau tiểu trâm 1 thân, cây cau tiểu trâm để bàn, cây cau tiểu trâm trang trí, cây cau tiểu trâm văn phòng</t>
+  </si>
+  <si>
+    <t>cây cau tiểu trâm, cau tiểu trâm 1 thân, cây cau tiểu trâm để bàn, cây cau tiểu trâm trang trí, cây cau tiểu trâm văn phòng, cây cảnh để bàn, cây cảnh văn phòng, cây nội thất xanh, cây trang trí nhà, cây xanh phong thủy</t>
+  </si>
+  <si>
+    <t>cây trầu bà đế vương xanh, trầu bà đế vương xanh để bàn, cây trầu bà đế vương văn phòng, cây trầu bà đế vương dễ chăm</t>
+  </si>
+  <si>
+    <t>cây trầu bà đế vương xanh, trầu bà đế vương xanh, trầu bà đế vương để bàn, cây trầu bà phong thủy, cây trầu bà trang trí, cây cảnh để bàn, cây cảnh văn phòng, cây nội thất xanh, cây dễ chăm sóc</t>
+  </si>
+  <si>
+    <t>cây trầu bà tỷ phú, trầu bà tỷ phú thủy sinh, cây trầu bà tỷ phú dễ sống, cây trầu bà tỷ phú giá tốt</t>
+  </si>
+  <si>
+    <t>cây trầu bà tỷ phú, trầu bà tỷ phú thủy sinh, cây trầu bà trồng nước, cây trầu bà dễ sống, cây trầu bà để bàn, cây thủy sinh trang trí, cây cảnh để bàn, cây cảnh văn phòng, cây nội thất xanh</t>
+  </si>
+  <si>
+    <t>cẩm tú mai thái, sứ thái lan, cây cẩm tú mai thái, cẩm tú mai thái dễ chăm</t>
+  </si>
+  <si>
+    <t>cẩm tú mai thái, sứ thái lan, cây cẩm tú mai, cây hoa cẩm tú mai, cây hoa cảnh đẹp, cây hoa cảnh dễ chăm, cây hoa trang trí, cây cảnh sân vườn, cây cảnh phong thủy, cây hoa giá tốt</t>
+  </si>
+  <si>
+    <t>hoa mười giờ sam thái, hoa mười giờ thái, cây hoa mười giờ dễ trồng, hoa mười giờ nắng đẹp</t>
+  </si>
+  <si>
+    <t>hoa mười giờ sam thái, hoa mười giờ thái, cây hoa mười giờ, hoa mười giờ nắng, hoa mười giờ dễ trồng, cây hoa cảnh nắng, cây hoa trồng chậu, cây hoa sân vườn, cây hoa trang trí, cây hoa giá tốt</t>
+  </si>
+  <si>
+    <t>cây phong lá đỏ để bàn, cây phong lá đỏ, cây phong lá đỏ trang trí, cây phong lá đỏ giá tốt</t>
+  </si>
+  <si>
+    <t>cây phong lá đỏ, cây phong lá đỏ để bàn, cây phong lá đỏ trang trí, cây phong lá đỏ mini, cây cảnh để bàn, cây cảnh trang trí, cây cảnh văn phòng, cây nội thất xanh, cây khỏe dễ chăm, cây cảnh giá tốt</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="163"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1125,17 +1810,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1440,33 +2117,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T11"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" customWidth="1"/>
-    <col min="3" max="3" width="60.21875" customWidth="1"/>
-    <col min="4" max="4" width="63.88671875" customWidth="1"/>
-    <col min="5" max="5" width="43.77734375" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.77734375" customWidth="1"/>
-    <col min="9" max="9" width="14.88671875" customWidth="1"/>
-    <col min="10" max="10" width="40.77734375" customWidth="1"/>
-    <col min="11" max="11" width="41.109375" customWidth="1"/>
-    <col min="12" max="12" width="36" customWidth="1"/>
-    <col min="13" max="13" width="58.33203125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="27.21875" customWidth="1"/>
-    <col min="15" max="15" width="29.77734375" customWidth="1"/>
-    <col min="16" max="16" width="39.88671875" customWidth="1"/>
-    <col min="17" max="17" width="31" customWidth="1"/>
-    <col min="18" max="18" width="19.44140625" customWidth="1"/>
-    <col min="19" max="19" width="16.88671875" customWidth="1"/>
-    <col min="20" max="20" width="15.44140625" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" customWidth="1"/>
+    <col min="2" max="2" width="63.44140625" customWidth="1"/>
+    <col min="3" max="3" width="47.88671875" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" customWidth="1"/>
+    <col min="5" max="5" width="41.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" customWidth="1"/>
+    <col min="10" max="10" width="46.5546875" customWidth="1"/>
+    <col min="11" max="11" width="40.33203125" customWidth="1"/>
+    <col min="12" max="12" width="24.109375" customWidth="1"/>
+    <col min="13" max="13" width="31.5546875" customWidth="1"/>
+    <col min="14" max="14" width="31.33203125" customWidth="1"/>
+    <col min="15" max="15" width="24.77734375" customWidth="1"/>
+    <col min="16" max="16" width="47" customWidth="1"/>
+    <col min="17" max="17" width="49.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1503,7 +2175,7 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
@@ -1528,7 +2200,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1562,20 +2234,20 @@
       <c r="L2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>73</v>
+      <c r="M2" t="s">
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1587,18 +2259,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>75</v>
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
       </c>
       <c r="F3">
         <v>350000</v>
@@ -1613,28 +2285,28 @@
         <v>100</v>
       </c>
       <c r="J3" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>79</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>82</v>
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P3" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1646,18 +2318,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>191</v>
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
       </c>
       <c r="F4">
         <v>400000</v>
@@ -1672,61 +2344,1225 @@
         <v>100</v>
       </c>
       <c r="J4" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="L4" t="s">
-        <v>141</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>190</v>
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5">
+        <v>50000</v>
+      </c>
+      <c r="G5">
+        <v>9900</v>
+      </c>
+      <c r="H5">
+        <v>2000</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" t="s">
+        <v>291</v>
+      </c>
+      <c r="N5" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>60</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6">
+        <v>45000</v>
+      </c>
+      <c r="G6">
+        <v>36000</v>
+      </c>
+      <c r="H6">
+        <v>22500</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K6" t="s">
+        <v>230</v>
+      </c>
+      <c r="L6" t="s">
+        <v>314</v>
+      </c>
+      <c r="M6" t="s">
+        <v>292</v>
+      </c>
+      <c r="N6" t="s">
         <v>27</v>
       </c>
-      <c r="P4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="2"/>
+      <c r="O6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" t="s">
+        <v>315</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F7">
+        <v>61600</v>
+      </c>
+      <c r="G7">
+        <v>49280</v>
+      </c>
+      <c r="H7">
+        <v>30800</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K7" t="s">
+        <v>231</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M7" t="s">
+        <v>293</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" t="s">
+        <v>316</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F8">
+        <v>79000</v>
+      </c>
+      <c r="G8">
+        <v>63200</v>
+      </c>
+      <c r="H8">
+        <v>39500</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K8" t="s">
+        <v>232</v>
+      </c>
+      <c r="L8" t="s">
+        <v>317</v>
+      </c>
+      <c r="M8" t="s">
+        <v>294</v>
+      </c>
+      <c r="N8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" t="s">
+        <v>318</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9">
+        <v>98000</v>
+      </c>
+      <c r="G9">
+        <v>78400</v>
+      </c>
+      <c r="H9">
+        <v>49000</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K9" t="s">
+        <v>233</v>
+      </c>
+      <c r="L9" t="s">
+        <v>319</v>
+      </c>
+      <c r="M9" t="s">
+        <v>295</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" t="s">
+        <v>320</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F10">
+        <v>24000</v>
+      </c>
+      <c r="G10">
+        <v>19200</v>
+      </c>
+      <c r="H10">
+        <v>12000</v>
+      </c>
+      <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="K10" t="s">
+        <v>234</v>
+      </c>
+      <c r="L10" t="s">
+        <v>321</v>
+      </c>
+      <c r="M10" t="s">
+        <v>296</v>
+      </c>
+      <c r="N10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" t="s">
+        <v>322</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F11">
+        <v>100000</v>
+      </c>
+      <c r="G11">
+        <v>80000</v>
+      </c>
+      <c r="H11">
+        <v>50000</v>
+      </c>
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="K11" t="s">
+        <v>235</v>
+      </c>
+      <c r="L11" t="s">
+        <v>323</v>
+      </c>
+      <c r="M11" t="s">
+        <v>297</v>
+      </c>
+      <c r="N11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" t="s">
+        <v>324</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F12">
+        <v>25000</v>
+      </c>
+      <c r="G12">
+        <v>20000</v>
+      </c>
+      <c r="H12">
+        <v>12500</v>
+      </c>
+      <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K12" t="s">
+        <v>236</v>
+      </c>
+      <c r="L12" t="s">
+        <v>325</v>
+      </c>
+      <c r="M12" t="s">
+        <v>298</v>
+      </c>
+      <c r="N12" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" t="s">
+        <v>326</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F13">
+        <v>69000</v>
+      </c>
+      <c r="G13">
+        <v>55200</v>
+      </c>
+      <c r="H13">
+        <v>34500</v>
+      </c>
+      <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K13" t="s">
+        <v>237</v>
+      </c>
+      <c r="L13" t="s">
+        <v>327</v>
+      </c>
+      <c r="M13" t="s">
+        <v>299</v>
+      </c>
+      <c r="N13" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" t="s">
+        <v>328</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>275</v>
+      </c>
+      <c r="B14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C14" t="s">
+        <v>259</v>
+      </c>
+      <c r="F14">
+        <v>35000</v>
+      </c>
+      <c r="G14">
+        <v>28000</v>
+      </c>
+      <c r="H14">
+        <v>17500</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K14" t="s">
+        <v>238</v>
+      </c>
+      <c r="L14" t="s">
+        <v>329</v>
+      </c>
+      <c r="M14" t="s">
+        <v>300</v>
+      </c>
+      <c r="N14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" t="s">
+        <v>330</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" t="s">
+        <v>260</v>
+      </c>
+      <c r="F15">
+        <v>67500</v>
+      </c>
+      <c r="G15">
+        <v>54000</v>
+      </c>
+      <c r="H15">
+        <v>33750</v>
+      </c>
+      <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="K15" t="s">
+        <v>239</v>
+      </c>
+      <c r="L15" t="s">
+        <v>331</v>
+      </c>
+      <c r="M15" t="s">
+        <v>301</v>
+      </c>
+      <c r="N15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" t="s">
+        <v>332</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C16" t="s">
+        <v>261</v>
+      </c>
+      <c r="F16">
+        <v>17000</v>
+      </c>
+      <c r="G16">
+        <v>13600</v>
+      </c>
+      <c r="H16">
+        <v>8500</v>
+      </c>
+      <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K16" t="s">
+        <v>240</v>
+      </c>
+      <c r="L16" t="s">
+        <v>333</v>
+      </c>
+      <c r="M16" t="s">
+        <v>310</v>
+      </c>
+      <c r="N16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" t="s">
+        <v>334</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>279</v>
+      </c>
+      <c r="B17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17">
+        <v>200000</v>
+      </c>
+      <c r="G17">
+        <v>160000</v>
+      </c>
+      <c r="H17">
+        <v>100000</v>
+      </c>
+      <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="K17" t="s">
+        <v>241</v>
+      </c>
+      <c r="L17" t="s">
+        <v>335</v>
+      </c>
+      <c r="M17" t="s">
+        <v>311</v>
+      </c>
+      <c r="N17" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" t="s">
+        <v>336</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>281</v>
+      </c>
+      <c r="B18" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18" t="s">
+        <v>309</v>
+      </c>
+      <c r="F18">
+        <v>25000</v>
+      </c>
+      <c r="G18">
+        <v>20000</v>
+      </c>
+      <c r="H18">
+        <v>12500</v>
+      </c>
+      <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="K18" t="s">
+        <v>242</v>
+      </c>
+      <c r="L18" t="s">
+        <v>337</v>
+      </c>
+      <c r="M18" t="s">
+        <v>313</v>
+      </c>
+      <c r="N18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" t="s">
+        <v>338</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" t="s">
+        <v>263</v>
+      </c>
+      <c r="F19">
+        <v>97000</v>
+      </c>
+      <c r="G19">
+        <v>77600</v>
+      </c>
+      <c r="H19">
+        <v>48500</v>
+      </c>
+      <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="K19" t="s">
+        <v>243</v>
+      </c>
+      <c r="L19" t="s">
+        <v>339</v>
+      </c>
+      <c r="M19" t="s">
+        <v>302</v>
+      </c>
+      <c r="N19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" t="s">
+        <v>340</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F20">
+        <v>30000</v>
+      </c>
+      <c r="G20">
+        <v>24000</v>
+      </c>
+      <c r="H20">
+        <v>15000</v>
+      </c>
+      <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="K20" t="s">
+        <v>244</v>
+      </c>
+      <c r="L20" t="s">
+        <v>341</v>
+      </c>
+      <c r="M20" t="s">
+        <v>303</v>
+      </c>
+      <c r="N20" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" t="s">
+        <v>342</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" t="s">
+        <v>265</v>
+      </c>
+      <c r="F21">
+        <v>30000</v>
+      </c>
+      <c r="G21">
+        <v>24000</v>
+      </c>
+      <c r="H21">
+        <v>15000</v>
+      </c>
+      <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="K21" t="s">
+        <v>245</v>
+      </c>
+      <c r="L21" t="s">
+        <v>343</v>
+      </c>
+      <c r="M21" t="s">
+        <v>304</v>
+      </c>
+      <c r="N21" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" t="s">
+        <v>344</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" t="s">
+        <v>266</v>
+      </c>
+      <c r="F22">
+        <v>20000</v>
+      </c>
+      <c r="G22">
+        <v>16000</v>
+      </c>
+      <c r="H22">
+        <v>10000</v>
+      </c>
+      <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K22" t="s">
+        <v>246</v>
+      </c>
+      <c r="L22" t="s">
+        <v>345</v>
+      </c>
+      <c r="M22" t="s">
+        <v>305</v>
+      </c>
+      <c r="N22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" t="s">
+        <v>346</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B23" t="s">
+        <v>226</v>
+      </c>
+      <c r="C23" t="s">
+        <v>267</v>
+      </c>
+      <c r="F23">
+        <v>78000</v>
+      </c>
+      <c r="G23">
+        <v>62400</v>
+      </c>
+      <c r="H23">
+        <v>39000</v>
+      </c>
+      <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K23" t="s">
+        <v>247</v>
+      </c>
+      <c r="L23" t="s">
+        <v>347</v>
+      </c>
+      <c r="M23" t="s">
+        <v>312</v>
+      </c>
+      <c r="N23" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" t="s">
+        <v>348</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>278</v>
+      </c>
+      <c r="B24" t="s">
+        <v>227</v>
+      </c>
+      <c r="C24" t="s">
+        <v>268</v>
+      </c>
+      <c r="F24">
+        <v>58000</v>
+      </c>
+      <c r="G24">
+        <v>46400</v>
+      </c>
+      <c r="H24">
+        <v>29000</v>
+      </c>
+      <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K24" t="s">
+        <v>248</v>
+      </c>
+      <c r="L24" t="s">
+        <v>349</v>
+      </c>
+      <c r="M24" t="s">
+        <v>306</v>
+      </c>
+      <c r="N24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" t="s">
+        <v>350</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25" t="s">
+        <v>269</v>
+      </c>
+      <c r="F25">
+        <v>32000</v>
+      </c>
+      <c r="G25">
+        <v>25600</v>
+      </c>
+      <c r="H25">
+        <v>16000</v>
+      </c>
+      <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="K25" t="s">
+        <v>249</v>
+      </c>
+      <c r="L25" t="s">
+        <v>351</v>
+      </c>
+      <c r="M25" t="s">
+        <v>307</v>
+      </c>
+      <c r="N25" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" t="s">
+        <v>352</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>286</v>
+      </c>
+      <c r="B26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C26" t="s">
+        <v>270</v>
+      </c>
+      <c r="F26">
+        <v>210222</v>
+      </c>
+      <c r="G26">
+        <v>168177</v>
+      </c>
+      <c r="H26">
+        <v>105111</v>
+      </c>
+      <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="K26" t="s">
+        <v>250</v>
+      </c>
+      <c r="L26" t="s">
+        <v>353</v>
+      </c>
+      <c r="M26" t="s">
+        <v>308</v>
+      </c>
+      <c r="N26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" t="s">
+        <v>354</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="34.21875" customWidth="1"/>
-    <col min="4" max="4" width="49.109375" customWidth="1"/>
-    <col min="6" max="6" width="48.33203125" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="62.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -1734,25 +3570,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F1" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="H1" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1760,10 +3596,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
         <v>21</v>
@@ -1773,9 +3609,6 @@
       </c>
       <c r="G2">
         <v>1</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1783,10 +3616,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -1803,10 +3636,10 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -1823,10 +3656,10 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
@@ -1840,39 +3673,36 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1880,19 +3710,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1900,19 +3730,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1923,42 +3753,39 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>178</v>
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="G10">
         <v>1</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>179</v>
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1966,19 +3793,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>177</v>
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1986,19 +3813,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>180</v>
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="H13">
         <v>3</v>
@@ -2006,19 +3833,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>187</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>181</v>
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -2026,54 +3853,60 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>182</v>
+        <v>94</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="H15">
         <v>5</v>
       </c>
     </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24.88671875" customWidth="1"/>
-    <col min="2" max="2" width="46.21875" customWidth="1"/>
-    <col min="3" max="3" width="70.77734375" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -2081,13 +3914,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2095,10 +3925,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2109,10 +3939,10 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2123,10 +3953,10 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2137,10 +3967,10 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2151,10 +3981,10 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2165,10 +3995,10 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -2179,10 +4009,10 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -2193,10 +4023,10 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -2207,10 +4037,10 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>9</v>
@@ -2218,27 +4048,24 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2246,13 +4073,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -2260,13 +4087,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -2274,13 +4101,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -2288,27 +4115,27 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>105</v>
+        <v>131</v>
+      </c>
+      <c r="C18" t="s">
+        <v>132</v>
       </c>
       <c r="D18">
         <v>6</v>
@@ -2316,13 +4143,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2330,13 +4157,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -2344,13 +4171,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -2358,13 +4185,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="D22">
         <v>10</v>
@@ -2372,13 +4199,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="D23">
         <v>11</v>
@@ -2386,13 +4213,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="D24">
         <v>12</v>
@@ -2400,13 +4227,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D25">
         <v>13</v>
@@ -2414,13 +4241,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="D26">
         <v>14</v>
@@ -2428,13 +4255,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="D27">
         <v>15</v>
@@ -2442,13 +4269,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="D28">
         <v>16</v>
@@ -2456,13 +4283,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="D29">
         <v>17</v>
@@ -2470,13 +4297,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="D30">
         <v>18</v>
@@ -2484,13 +4311,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="D31">
         <v>19</v>
@@ -2498,27 +4325,24 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C33" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2526,13 +4350,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -2540,13 +4364,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C35" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -2554,13 +4378,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -2568,13 +4392,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -2582,13 +4406,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -2596,13 +4420,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="C39" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="D39">
         <v>7</v>
@@ -2610,13 +4434,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C40" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D40">
         <v>8</v>
@@ -2624,13 +4448,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D41">
         <v>9</v>
@@ -2638,13 +4462,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C42" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D42">
         <v>10</v>
@@ -2652,13 +4476,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="C43" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D43">
         <v>11</v>
@@ -2666,13 +4490,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D44">
         <v>12</v>
@@ -2680,13 +4504,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="D45">
         <v>13</v>
@@ -2694,53 +4518,43 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="D46">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="2" max="2" width="54.109375" customWidth="1"/>
-    <col min="3" max="3" width="61" customWidth="1"/>
-    <col min="4" max="4" width="42.5546875" customWidth="1"/>
-    <col min="5" max="5" width="38.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>189</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="F1" t="s">
         <v>18</v>
@@ -2751,16 +4565,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2768,19 +4582,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2788,22 +4602,67 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="E4" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="F4">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
